--- a/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_tobacco.xlsx
+++ b/research/traditional_assets/database/data/palestinian_authority/palestinian_authority_tobacco.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="plse_jcc" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,115 +590,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.109</v>
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="E2">
+        <v>0.285</v>
       </c>
       <c r="G2">
-        <v>0.04809110629067245</v>
+        <v>0.04614614614614615</v>
       </c>
       <c r="H2">
-        <v>0.04436008676789588</v>
+        <v>0.04614614614614615</v>
       </c>
       <c r="I2">
-        <v>0.04067245119305857</v>
+        <v>0.01731731731731732</v>
       </c>
       <c r="J2">
-        <v>0.03848551142762811</v>
+        <v>0.01484732100521574</v>
       </c>
       <c r="K2">
-        <v>6.49</v>
+        <v>1.7</v>
       </c>
       <c r="L2">
-        <v>0.07039045553145336</v>
+        <v>0.01701701701701702</v>
       </c>
       <c r="M2">
-        <v>1.426</v>
+        <v>1.69</v>
       </c>
       <c r="N2">
-        <v>0.06068085106382978</v>
+        <v>0.05807560137457044</v>
       </c>
       <c r="O2">
-        <v>0.2197226502311248</v>
+        <v>0.9941176470588236</v>
       </c>
       <c r="P2">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="Q2">
-        <v>0.06</v>
+        <v>0.05807560137457044</v>
       </c>
       <c r="R2">
-        <v>0.2172573189522342</v>
+        <v>0.9941176470588236</v>
       </c>
       <c r="S2">
-        <v>0.01600000000000001</v>
+        <v>0</v>
       </c>
       <c r="T2">
-        <v>0.0112201963534362</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>3.09</v>
+        <v>4.61</v>
       </c>
       <c r="V2">
-        <v>0.1314893617021277</v>
+        <v>0.1584192439862543</v>
       </c>
       <c r="W2">
-        <v>0.233453237410072</v>
+        <v>0.04956268221574344</v>
       </c>
       <c r="X2">
-        <v>0.1404458681290134</v>
+        <v>0.1431003572966232</v>
       </c>
       <c r="Y2">
-        <v>0.09300736928105857</v>
+        <v>-0.09353767508087973</v>
       </c>
       <c r="Z2">
-        <v>2.232445520581114</v>
+        <v>2.147925177381209</v>
       </c>
       <c r="AA2">
-        <v>0.08591680759388162</v>
+        <v>0.03189093460376377</v>
       </c>
       <c r="AB2">
-        <v>0.1094018814961633</v>
+        <v>0.1047063455772662</v>
       </c>
       <c r="AC2">
-        <v>-0.02348507390228166</v>
+        <v>-0.07281541097350247</v>
       </c>
       <c r="AD2">
-        <v>15.3</v>
+        <v>23.2</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.3</v>
+        <v>23.2</v>
       </c>
       <c r="AG2">
-        <v>12.21</v>
+        <v>18.59</v>
       </c>
       <c r="AH2">
-        <v>0.3943298969072165</v>
+        <v>0.4435946462715105</v>
       </c>
       <c r="AI2">
-        <v>0.2761732851985559</v>
+        <v>0.3772357723577235</v>
       </c>
       <c r="AJ2">
-        <v>0.3419210305236628</v>
+        <v>0.3898091843153701</v>
       </c>
       <c r="AK2">
-        <v>0.2334161728159052</v>
+        <v>0.3267709615046581</v>
       </c>
       <c r="AL2">
-        <v>0</v>
+        <v>0.106</v>
       </c>
       <c r="AM2">
-        <v>-0.027</v>
+        <v>-0.015</v>
       </c>
       <c r="AN2">
-        <v>3.26923076923077</v>
+        <v>7.864406779661016</v>
+      </c>
+      <c r="AO2">
+        <v>16.32075471698113</v>
       </c>
       <c r="AP2">
-        <v>2.608974358974359</v>
+        <v>6.301694915254237</v>
       </c>
       <c r="AQ2">
-        <v>-138.8888888888889</v>
+        <v>-115.3333333333333</v>
       </c>
     </row>
     <row r="3">
@@ -716,115 +724,8893 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.109</v>
+        <v>0.09329999999999999</v>
+      </c>
+      <c r="E3">
+        <v>0.285</v>
       </c>
       <c r="G3">
-        <v>0.04809110629067245</v>
+        <v>0.04614614614614615</v>
       </c>
       <c r="H3">
-        <v>0.04436008676789588</v>
+        <v>0.04614614614614615</v>
       </c>
       <c r="I3">
-        <v>0.04067245119305857</v>
+        <v>0.01731731731731732</v>
       </c>
       <c r="J3">
-        <v>0.03848551142762811</v>
+        <v>0.01484732100521574</v>
       </c>
       <c r="K3">
-        <v>6.49</v>
+        <v>1.7</v>
       </c>
       <c r="L3">
-        <v>0.07039045553145336</v>
+        <v>0.01701701701701702</v>
       </c>
       <c r="M3">
-        <v>1.426</v>
+        <v>1.69</v>
       </c>
       <c r="N3">
-        <v>0.06068085106382978</v>
+        <v>0.05807560137457044</v>
       </c>
       <c r="O3">
-        <v>0.2197226502311248</v>
+        <v>0.9941176470588236</v>
       </c>
       <c r="P3">
-        <v>1.41</v>
+        <v>1.69</v>
       </c>
       <c r="Q3">
+        <v>0.05807560137457044</v>
+      </c>
+      <c r="R3">
+        <v>0.9941176470588236</v>
+      </c>
+      <c r="S3">
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>4.61</v>
+      </c>
+      <c r="V3">
+        <v>0.1584192439862543</v>
+      </c>
+      <c r="W3">
+        <v>0.04956268221574344</v>
+      </c>
+      <c r="X3">
+        <v>0.1431003572966232</v>
+      </c>
+      <c r="Y3">
+        <v>-0.09353767508087973</v>
+      </c>
+      <c r="Z3">
+        <v>2.147925177381209</v>
+      </c>
+      <c r="AA3">
+        <v>0.03189093460376377</v>
+      </c>
+      <c r="AB3">
+        <v>0.1047063455772662</v>
+      </c>
+      <c r="AC3">
+        <v>-0.07281541097350247</v>
+      </c>
+      <c r="AD3">
+        <v>23.2</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>23.2</v>
+      </c>
+      <c r="AG3">
+        <v>18.59</v>
+      </c>
+      <c r="AH3">
+        <v>0.4435946462715105</v>
+      </c>
+      <c r="AI3">
+        <v>0.3772357723577235</v>
+      </c>
+      <c r="AJ3">
+        <v>0.3898091843153701</v>
+      </c>
+      <c r="AK3">
+        <v>0.3267709615046581</v>
+      </c>
+      <c r="AL3">
+        <v>0.106</v>
+      </c>
+      <c r="AM3">
+        <v>-0.015</v>
+      </c>
+      <c r="AN3">
+        <v>7.864406779661016</v>
+      </c>
+      <c r="AO3">
+        <v>16.32075471698113</v>
+      </c>
+      <c r="AP3">
+        <v>6.301694915254237</v>
+      </c>
+      <c r="AQ3">
+        <v>-115.3333333333333</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Jerusalem Cigarette Co. Ltd. (PLSE:JCC)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PLSE:JCC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Tobacco</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Palestinian Authority</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>16.3207547169811</v>
+      </c>
+      <c r="F2">
+        <v>4.64193009843575</v>
+      </c>
+      <c r="G2">
+        <v>7.86440677966102</v>
+      </c>
+      <c r="H2">
+        <v>2.48203389830508</v>
+      </c>
+      <c r="I2">
+        <v>0.443594646271511</v>
+      </c>
+      <c r="J2">
+        <v>0.14</v>
+      </c>
+      <c r="K2">
+        <v>29.1</v>
+      </c>
+      <c r="L2">
+        <v>47.9862246476866</v>
+      </c>
+      <c r="M2">
+        <v>47.69</v>
+      </c>
+      <c r="N2">
+        <v>50.6982246476866</v>
+      </c>
+      <c r="O2">
+        <v>23.2</v>
+      </c>
+      <c r="P2">
+        <v>7.322</v>
+      </c>
+      <c r="Q2">
+        <v>0.104706345577266</v>
+      </c>
+      <c r="R2">
+        <v>0.100795733428966</v>
+      </c>
+      <c r="S2">
+        <v>0.0565483394982453</v>
+      </c>
+      <c r="T2">
+        <v>0.0413510825538098</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.143100357296623</v>
+      </c>
+      <c r="X2">
+        <v>0.110472769617945</v>
+      </c>
+      <c r="Y2">
+        <v>0.918217850684933</v>
+      </c>
+      <c r="Z2">
+        <v>0.630977862176095</v>
+      </c>
+      <c r="AA2">
+        <v>23.2</v>
+      </c>
+      <c r="AB2">
+        <v>0.06960665362787447</v>
+      </c>
+      <c r="AC2">
+        <v>16.32075471698113</v>
+      </c>
+      <c r="AD2">
+        <v>23.2</v>
+      </c>
+      <c r="AE2">
+        <v>0.106</v>
+      </c>
+      <c r="AF2">
+        <v>1.22</v>
+      </c>
+      <c r="AG2">
+        <v>2.95</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>29.1</v>
+      </c>
+      <c r="AK2">
+        <v>0.1135899908924898</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>2.44</v>
+      </c>
+      <c r="AR2">
+        <v>0.106</v>
+      </c>
+      <c r="AS2">
+        <v>23.2</v>
+      </c>
+      <c r="AT2">
+        <v>4.61</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1021011364019903</v>
+      </c>
+      <c r="C2">
+        <v>54.2627203022062</v>
+      </c>
+      <c r="D2">
+        <v>49.65272030220621</v>
+      </c>
+      <c r="E2">
+        <v>-23.2</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>4.61</v>
+      </c>
+      <c r="H2">
+        <v>29.1</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>2.95</v>
+      </c>
+      <c r="K2">
+        <v>1.22</v>
+      </c>
+      <c r="L2">
+        <v>1.73</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1.73</v>
+      </c>
+      <c r="O2">
+        <v>0.3245506322575437</v>
+      </c>
+      <c r="P2">
+        <v>1.405449367742456</v>
+      </c>
+      <c r="Q2">
+        <v>2.625449367742457</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1021011364019903</v>
+      </c>
+      <c r="T2">
+        <v>0.5572774141861078</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W2">
+        <v>0.03631421198733399</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1019575246268238</v>
+      </c>
+      <c r="C3">
+        <v>53.85262395615047</v>
+      </c>
+      <c r="D3">
+        <v>49.76562395615048</v>
+      </c>
+      <c r="E3">
+        <v>-22.677</v>
+      </c>
+      <c r="F3">
+        <v>0.523</v>
+      </c>
+      <c r="G3">
+        <v>4.61</v>
+      </c>
+      <c r="H3">
+        <v>29.1</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>2.95</v>
+      </c>
+      <c r="K3">
+        <v>1.22</v>
+      </c>
+      <c r="L3">
+        <v>1.73</v>
+      </c>
+      <c r="M3">
+        <v>0.0233781</v>
+      </c>
+      <c r="N3">
+        <v>1.7066219</v>
+      </c>
+      <c r="O3">
+        <v>0.3201648651269194</v>
+      </c>
+      <c r="P3">
+        <v>1.386457034873081</v>
+      </c>
+      <c r="Q3">
+        <v>2.606457034873081</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1026205883908591</v>
+      </c>
+      <c r="T3">
+        <v>0.5618504578564821</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W3">
+        <v>0.03631421198733399</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>74.00088116656187</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1018139128516573</v>
+      </c>
+      <c r="C4">
+        <v>53.44304223594267</v>
+      </c>
+      <c r="D4">
+        <v>49.87904223594267</v>
+      </c>
+      <c r="E4">
+        <v>-22.154</v>
+      </c>
+      <c r="F4">
+        <v>1.046</v>
+      </c>
+      <c r="G4">
+        <v>4.61</v>
+      </c>
+      <c r="H4">
+        <v>29.1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>2.95</v>
+      </c>
+      <c r="K4">
+        <v>1.22</v>
+      </c>
+      <c r="L4">
+        <v>1.73</v>
+      </c>
+      <c r="M4">
+        <v>0.0467562</v>
+      </c>
+      <c r="N4">
+        <v>1.6832438</v>
+      </c>
+      <c r="O4">
+        <v>0.3157790979962951</v>
+      </c>
+      <c r="P4">
+        <v>1.367464702003705</v>
+      </c>
+      <c r="Q4">
+        <v>2.587464702003705</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1031506414407252</v>
+      </c>
+      <c r="T4">
+        <v>0.5665168289487009</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W4">
+        <v>0.03631421198733399</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>37.00044058328093</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1016703010764909</v>
+      </c>
+      <c r="C5">
+        <v>53.03397866819217</v>
+      </c>
+      <c r="D5">
+        <v>49.99297866819217</v>
+      </c>
+      <c r="E5">
+        <v>-21.631</v>
+      </c>
+      <c r="F5">
+        <v>1.569</v>
+      </c>
+      <c r="G5">
+        <v>4.61</v>
+      </c>
+      <c r="H5">
+        <v>29.1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>2.95</v>
+      </c>
+      <c r="K5">
+        <v>1.22</v>
+      </c>
+      <c r="L5">
+        <v>1.73</v>
+      </c>
+      <c r="M5">
+        <v>0.0701343</v>
+      </c>
+      <c r="N5">
+        <v>1.6598657</v>
+      </c>
+      <c r="O5">
+        <v>0.3113933308656707</v>
+      </c>
+      <c r="P5">
+        <v>1.348472369134329</v>
+      </c>
+      <c r="Q5">
+        <v>2.568472369134329</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1036916234194545</v>
+      </c>
+      <c r="T5">
+        <v>0.5712794138778725</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W5">
+        <v>0.03631421198733399</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>24.66696038885395</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1015266893013244</v>
+      </c>
+      <c r="C6">
+        <v>52.62543681180484</v>
+      </c>
+      <c r="D6">
+        <v>50.10743681180484</v>
+      </c>
+      <c r="E6">
+        <v>-21.108</v>
+      </c>
+      <c r="F6">
+        <v>2.092</v>
+      </c>
+      <c r="G6">
+        <v>4.61</v>
+      </c>
+      <c r="H6">
+        <v>29.1</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>2.95</v>
+      </c>
+      <c r="K6">
+        <v>1.22</v>
+      </c>
+      <c r="L6">
+        <v>1.73</v>
+      </c>
+      <c r="M6">
+        <v>0.09351240000000001</v>
+      </c>
+      <c r="N6">
+        <v>1.6364876</v>
+      </c>
+      <c r="O6">
+        <v>0.3070075637350464</v>
+      </c>
+      <c r="P6">
+        <v>1.329480036264953</v>
+      </c>
+      <c r="Q6">
+        <v>2.549480036264954</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.104243875856074</v>
+      </c>
+      <c r="T6">
+        <v>0.5761412193264021</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W6">
+        <v>0.03631421198733399</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>18.50022029164046</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1013830775261579</v>
+      </c>
+      <c r="C7">
+        <v>52.2174202583536</v>
+      </c>
+      <c r="D7">
+        <v>50.2224202583536</v>
+      </c>
+      <c r="E7">
+        <v>-20.585</v>
+      </c>
+      <c r="F7">
+        <v>2.615</v>
+      </c>
+      <c r="G7">
+        <v>4.61</v>
+      </c>
+      <c r="H7">
+        <v>29.1</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>2.95</v>
+      </c>
+      <c r="K7">
+        <v>1.22</v>
+      </c>
+      <c r="L7">
+        <v>1.73</v>
+      </c>
+      <c r="M7">
+        <v>0.1168905</v>
+      </c>
+      <c r="N7">
+        <v>1.6131095</v>
+      </c>
+      <c r="O7">
+        <v>0.3026217966044221</v>
+      </c>
+      <c r="P7">
+        <v>1.310487703395578</v>
+      </c>
+      <c r="Q7">
+        <v>2.530487703395578</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1048077546597802</v>
+      </c>
+      <c r="T7">
+        <v>0.5811053785738478</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W7">
+        <v>0.03631421198733399</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>14.80017623331237</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
         <v>0.06</v>
       </c>
-      <c r="R3">
-        <v>0.2172573189522342</v>
-      </c>
-      <c r="S3">
-        <v>0.01600000000000001</v>
-      </c>
-      <c r="T3">
-        <v>0.0112201963534362</v>
-      </c>
-      <c r="U3">
-        <v>3.09</v>
-      </c>
-      <c r="V3">
-        <v>0.1314893617021277</v>
-      </c>
-      <c r="W3">
-        <v>0.233453237410072</v>
-      </c>
-      <c r="X3">
-        <v>0.1404458681290134</v>
-      </c>
-      <c r="Y3">
-        <v>0.09300736928105857</v>
-      </c>
-      <c r="Z3">
-        <v>2.232445520581114</v>
-      </c>
-      <c r="AA3">
-        <v>0.08591680759388162</v>
-      </c>
-      <c r="AB3">
-        <v>0.1094018814961633</v>
-      </c>
-      <c r="AC3">
-        <v>-0.02348507390228166</v>
-      </c>
-      <c r="AD3">
-        <v>15.3</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>15.3</v>
-      </c>
-      <c r="AG3">
-        <v>12.21</v>
-      </c>
-      <c r="AH3">
-        <v>0.3943298969072165</v>
-      </c>
-      <c r="AI3">
-        <v>0.2761732851985559</v>
-      </c>
-      <c r="AJ3">
-        <v>0.3419210305236628</v>
-      </c>
-      <c r="AK3">
-        <v>0.2334161728159052</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>-0.027</v>
-      </c>
-      <c r="AN3">
-        <v>3.26923076923077</v>
-      </c>
-      <c r="AP3">
-        <v>2.608974358974359</v>
-      </c>
-      <c r="AQ3">
-        <v>-138.8888888888889</v>
+      <c r="B8">
+        <v>0.1012930840505701</v>
+      </c>
+      <c r="C8">
+        <v>51.76674330369772</v>
+      </c>
+      <c r="D8">
+        <v>50.29474330369771</v>
+      </c>
+      <c r="E8">
+        <v>-20.062</v>
+      </c>
+      <c r="F8">
+        <v>3.138</v>
+      </c>
+      <c r="G8">
+        <v>4.61</v>
+      </c>
+      <c r="H8">
+        <v>29.1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>2.95</v>
+      </c>
+      <c r="K8">
+        <v>1.22</v>
+      </c>
+      <c r="L8">
+        <v>1.73</v>
+      </c>
+      <c r="M8">
+        <v>0.1437204</v>
+      </c>
+      <c r="N8">
+        <v>1.5862796</v>
+      </c>
+      <c r="O8">
+        <v>0.2975884665417592</v>
+      </c>
+      <c r="P8">
+        <v>1.288691133458241</v>
+      </c>
+      <c r="Q8">
+        <v>2.508691133458241</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1053836308848419</v>
+      </c>
+      <c r="T8">
+        <v>0.5861751582308139</v>
+      </c>
+      <c r="U8">
+        <v>0.0458</v>
+      </c>
+      <c r="V8">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W8">
+        <v>0.03720785031364422</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>12.03726123779227</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.1011584086586667</v>
+      </c>
+      <c r="C9">
+        <v>51.35236480977527</v>
+      </c>
+      <c r="D9">
+        <v>50.40336480977528</v>
+      </c>
+      <c r="E9">
+        <v>-19.539</v>
+      </c>
+      <c r="F9">
+        <v>3.661</v>
+      </c>
+      <c r="G9">
+        <v>4.61</v>
+      </c>
+      <c r="H9">
+        <v>29.1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>2.95</v>
+      </c>
+      <c r="K9">
+        <v>1.22</v>
+      </c>
+      <c r="L9">
+        <v>1.73</v>
+      </c>
+      <c r="M9">
+        <v>0.1676738</v>
+      </c>
+      <c r="N9">
+        <v>1.5623262</v>
+      </c>
+      <c r="O9">
+        <v>0.2930947722557952</v>
+      </c>
+      <c r="P9">
+        <v>1.269231427744205</v>
+      </c>
+      <c r="Q9">
+        <v>2.489231427744205</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1059718915448512</v>
+      </c>
+      <c r="T9">
+        <v>0.5913539654072844</v>
+      </c>
+      <c r="U9">
+        <v>0.0458</v>
+      </c>
+      <c r="V9">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W9">
+        <v>0.03720785031364422</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>10.31765248953623</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.101166715398973</v>
+      </c>
+      <c r="C10">
+        <v>50.82265149066973</v>
+      </c>
+      <c r="D10">
+        <v>50.39665149066973</v>
+      </c>
+      <c r="E10">
+        <v>-19.016</v>
+      </c>
+      <c r="F10">
+        <v>4.184</v>
+      </c>
+      <c r="G10">
+        <v>4.61</v>
+      </c>
+      <c r="H10">
+        <v>29.1</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>2.95</v>
+      </c>
+      <c r="K10">
+        <v>1.22</v>
+      </c>
+      <c r="L10">
+        <v>1.73</v>
+      </c>
+      <c r="M10">
+        <v>0.200832</v>
+      </c>
+      <c r="N10">
+        <v>1.529168</v>
+      </c>
+      <c r="O10">
+        <v>0.2868742434843951</v>
+      </c>
+      <c r="P10">
+        <v>1.242293756515605</v>
+      </c>
+      <c r="Q10">
+        <v>2.462293756515605</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.106572940480078</v>
+      </c>
+      <c r="T10">
+        <v>0.5966453553484609</v>
+      </c>
+      <c r="U10">
+        <v>0.048</v>
+      </c>
+      <c r="V10">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W10">
+        <v>0.03899512696626468</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>8.614165073295091</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1011595865681884</v>
+      </c>
+      <c r="C11">
+        <v>50.30541274119041</v>
+      </c>
+      <c r="D11">
+        <v>50.40241274119041</v>
+      </c>
+      <c r="E11">
+        <v>-18.493</v>
+      </c>
+      <c r="F11">
+        <v>4.707</v>
+      </c>
+      <c r="G11">
+        <v>4.61</v>
+      </c>
+      <c r="H11">
+        <v>29.1</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>2.95</v>
+      </c>
+      <c r="K11">
+        <v>1.22</v>
+      </c>
+      <c r="L11">
+        <v>1.73</v>
+      </c>
+      <c r="M11">
+        <v>0.2329965</v>
+      </c>
+      <c r="N11">
+        <v>1.4970035</v>
+      </c>
+      <c r="O11">
+        <v>0.2808401343449455</v>
+      </c>
+      <c r="P11">
+        <v>1.216163365655054</v>
+      </c>
+      <c r="Q11">
+        <v>2.436163365655054</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1071871992820132</v>
+      </c>
+      <c r="T11">
+        <v>0.6020530395740589</v>
+      </c>
+      <c r="U11">
+        <v>0.0495</v>
+      </c>
+      <c r="V11">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W11">
+        <v>0.04021372468396046</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>7.425004238261089</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1010549699199882</v>
+      </c>
+      <c r="C12">
+        <v>49.86711170560986</v>
+      </c>
+      <c r="D12">
+        <v>50.48711170560986</v>
+      </c>
+      <c r="E12">
+        <v>-17.97</v>
+      </c>
+      <c r="F12">
+        <v>5.23</v>
+      </c>
+      <c r="G12">
+        <v>4.61</v>
+      </c>
+      <c r="H12">
+        <v>29.1</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>2.95</v>
+      </c>
+      <c r="K12">
+        <v>1.22</v>
+      </c>
+      <c r="L12">
+        <v>1.73</v>
+      </c>
+      <c r="M12">
+        <v>0.258885</v>
+      </c>
+      <c r="N12">
+        <v>1.471115</v>
+      </c>
+      <c r="O12">
+        <v>0.2759834123546568</v>
+      </c>
+      <c r="P12">
+        <v>1.195131587645343</v>
+      </c>
+      <c r="Q12">
+        <v>2.415131587645343</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1078151082795469</v>
+      </c>
+      <c r="T12">
+        <v>0.6075808945602257</v>
+      </c>
+      <c r="U12">
+        <v>0.0495</v>
+      </c>
+      <c r="V12">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W12">
+        <v>0.04021372468396046</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>6.68250381443498</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1010754626374715</v>
+      </c>
+      <c r="C13">
+        <v>49.32749812984647</v>
+      </c>
+      <c r="D13">
+        <v>50.47049812984647</v>
+      </c>
+      <c r="E13">
+        <v>-17.447</v>
+      </c>
+      <c r="F13">
+        <v>5.753</v>
+      </c>
+      <c r="G13">
+        <v>4.61</v>
+      </c>
+      <c r="H13">
+        <v>29.1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>2.95</v>
+      </c>
+      <c r="K13">
+        <v>1.22</v>
+      </c>
+      <c r="L13">
+        <v>1.73</v>
+      </c>
+      <c r="M13">
+        <v>0.2928277</v>
+      </c>
+      <c r="N13">
+        <v>1.4371723</v>
+      </c>
+      <c r="O13">
+        <v>0.2696157101896117</v>
+      </c>
+      <c r="P13">
+        <v>1.167556589810388</v>
+      </c>
+      <c r="Q13">
+        <v>2.387556589810388</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1084571275916319</v>
+      </c>
+      <c r="T13">
+        <v>0.6132329710067558</v>
+      </c>
+      <c r="U13">
+        <v>0.0509</v>
+      </c>
+      <c r="V13">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W13">
+        <v>0.04135108255380984</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>5.907911034372772</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1009822195679698</v>
+      </c>
+      <c r="C14">
+        <v>48.88017931648798</v>
+      </c>
+      <c r="D14">
+        <v>50.54617931648799</v>
+      </c>
+      <c r="E14">
+        <v>-16.924</v>
+      </c>
+      <c r="F14">
+        <v>6.276</v>
+      </c>
+      <c r="G14">
+        <v>4.61</v>
+      </c>
+      <c r="H14">
+        <v>29.1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>2.95</v>
+      </c>
+      <c r="K14">
+        <v>1.22</v>
+      </c>
+      <c r="L14">
+        <v>1.73</v>
+      </c>
+      <c r="M14">
+        <v>0.3194484</v>
+      </c>
+      <c r="N14">
+        <v>1.4105516</v>
+      </c>
+      <c r="O14">
+        <v>0.2646216263652543</v>
+      </c>
+      <c r="P14">
+        <v>1.145929973634746</v>
+      </c>
+      <c r="Q14">
+        <v>2.365929973634746</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1091137382517188</v>
+      </c>
+      <c r="T14">
+        <v>0.6190135037361616</v>
+      </c>
+      <c r="U14">
+        <v>0.0509</v>
+      </c>
+      <c r="V14">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W14">
+        <v>0.04135108255380984</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>5.415585114841708</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.100888976498468</v>
+      </c>
+      <c r="C15">
+        <v>48.43308781388718</v>
+      </c>
+      <c r="D15">
+        <v>50.62208781388718</v>
+      </c>
+      <c r="E15">
+        <v>-16.401</v>
+      </c>
+      <c r="F15">
+        <v>6.798999999999999</v>
+      </c>
+      <c r="G15">
+        <v>4.61</v>
+      </c>
+      <c r="H15">
+        <v>29.1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>2.95</v>
+      </c>
+      <c r="K15">
+        <v>1.22</v>
+      </c>
+      <c r="L15">
+        <v>1.73</v>
+      </c>
+      <c r="M15">
+        <v>0.3460691</v>
+      </c>
+      <c r="N15">
+        <v>1.3839309</v>
+      </c>
+      <c r="O15">
+        <v>0.2596275425408968</v>
+      </c>
+      <c r="P15">
+        <v>1.124303357459103</v>
+      </c>
+      <c r="Q15">
+        <v>2.344303357459103</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1097854434097388</v>
+      </c>
+      <c r="T15">
+        <v>0.6249269222754388</v>
+      </c>
+      <c r="U15">
+        <v>0.0509</v>
+      </c>
+      <c r="V15">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W15">
+        <v>0.04135108255380984</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>4.99900164446927</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1007957334289663</v>
+      </c>
+      <c r="C16">
+        <v>47.98622464768657</v>
+      </c>
+      <c r="D16">
+        <v>50.69822464768657</v>
+      </c>
+      <c r="E16">
+        <v>-15.878</v>
+      </c>
+      <c r="F16">
+        <v>7.322</v>
+      </c>
+      <c r="G16">
+        <v>4.61</v>
+      </c>
+      <c r="H16">
+        <v>29.1</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>2.95</v>
+      </c>
+      <c r="K16">
+        <v>1.22</v>
+      </c>
+      <c r="L16">
+        <v>1.73</v>
+      </c>
+      <c r="M16">
+        <v>0.3726898</v>
+      </c>
+      <c r="N16">
+        <v>1.3573102</v>
+      </c>
+      <c r="O16">
+        <v>0.2546334587165393</v>
+      </c>
+      <c r="P16">
+        <v>1.102676741283461</v>
+      </c>
+      <c r="Q16">
+        <v>2.322676741283461</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1104727696179453</v>
+      </c>
+      <c r="T16">
+        <v>0.6309778621760945</v>
+      </c>
+      <c r="U16">
+        <v>0.0509</v>
+      </c>
+      <c r="V16">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W16">
+        <v>0.04135108255380984</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>4.64193009843575</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1010193257660655</v>
+      </c>
+      <c r="C17">
+        <v>47.28103471881501</v>
+      </c>
+      <c r="D17">
+        <v>50.51603471881501</v>
+      </c>
+      <c r="E17">
+        <v>-15.355</v>
+      </c>
+      <c r="F17">
+        <v>7.844999999999999</v>
+      </c>
+      <c r="G17">
+        <v>4.61</v>
+      </c>
+      <c r="H17">
+        <v>29.1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>2.95</v>
+      </c>
+      <c r="K17">
+        <v>1.22</v>
+      </c>
+      <c r="L17">
+        <v>1.73</v>
+      </c>
+      <c r="M17">
+        <v>0.4197075</v>
+      </c>
+      <c r="N17">
+        <v>1.3102925</v>
+      </c>
+      <c r="O17">
+        <v>0.245812866657409</v>
+      </c>
+      <c r="P17">
+        <v>1.064479633342591</v>
+      </c>
+      <c r="Q17">
+        <v>2.284479633342591</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1111762682075213</v>
+      </c>
+      <c r="T17">
+        <v>0.6371711771332362</v>
+      </c>
+      <c r="U17">
+        <v>0.0535</v>
+      </c>
+      <c r="V17">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W17">
+        <v>0.04346331859781585</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>4.121918240679522</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.1012981611997002</v>
+      </c>
+      <c r="C18">
+        <v>46.53265752089523</v>
+      </c>
+      <c r="D18">
+        <v>50.29065752089523</v>
+      </c>
+      <c r="E18">
+        <v>-14.832</v>
+      </c>
+      <c r="F18">
+        <v>8.368</v>
+      </c>
+      <c r="G18">
+        <v>4.61</v>
+      </c>
+      <c r="H18">
+        <v>29.1</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>2.95</v>
+      </c>
+      <c r="K18">
+        <v>1.22</v>
+      </c>
+      <c r="L18">
+        <v>1.73</v>
+      </c>
+      <c r="M18">
+        <v>0.4702816</v>
+      </c>
+      <c r="N18">
+        <v>1.2597184</v>
+      </c>
+      <c r="O18">
+        <v>0.2363250885470874</v>
+      </c>
+      <c r="P18">
+        <v>1.023393311452912</v>
+      </c>
+      <c r="Q18">
+        <v>2.243393311452913</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1118965167635159</v>
+      </c>
+      <c r="T18">
+        <v>0.6435119519703099</v>
+      </c>
+      <c r="U18">
+        <v>0.0562</v>
+      </c>
+      <c r="V18">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W18">
+        <v>0.04565679448966824</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>3.678647006389363</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.1018970816338497</v>
+      </c>
+      <c r="C19">
+        <v>45.53229626018172</v>
+      </c>
+      <c r="D19">
+        <v>49.81329626018172</v>
+      </c>
+      <c r="E19">
+        <v>-14.309</v>
+      </c>
+      <c r="F19">
+        <v>8.891</v>
+      </c>
+      <c r="G19">
+        <v>4.61</v>
+      </c>
+      <c r="H19">
+        <v>29.1</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>2.95</v>
+      </c>
+      <c r="K19">
+        <v>1.22</v>
+      </c>
+      <c r="L19">
+        <v>1.73</v>
+      </c>
+      <c r="M19">
+        <v>0.5414619000000001</v>
+      </c>
+      <c r="N19">
+        <v>1.1885381</v>
+      </c>
+      <c r="O19">
+        <v>0.2229715559636877</v>
+      </c>
+      <c r="P19">
+        <v>0.9655665440363123</v>
+      </c>
+      <c r="Q19">
+        <v>2.185566544036313</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.1126341207064018</v>
+      </c>
+      <c r="T19">
+        <v>0.6500055165624937</v>
+      </c>
+      <c r="U19">
+        <v>0.0609</v>
+      </c>
+      <c r="V19">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W19">
+        <v>0.04947506733844832</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>3.195053982560915</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.1018850784121944</v>
+      </c>
+      <c r="C20">
+        <v>45.01877425484292</v>
+      </c>
+      <c r="D20">
+        <v>49.82277425484293</v>
+      </c>
+      <c r="E20">
+        <v>-13.786</v>
+      </c>
+      <c r="F20">
+        <v>9.414</v>
+      </c>
+      <c r="G20">
+        <v>4.61</v>
+      </c>
+      <c r="H20">
+        <v>29.1</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>2.95</v>
+      </c>
+      <c r="K20">
+        <v>1.22</v>
+      </c>
+      <c r="L20">
+        <v>1.73</v>
+      </c>
+      <c r="M20">
+        <v>0.5733126000000001</v>
+      </c>
+      <c r="N20">
+        <v>1.1566874</v>
+      </c>
+      <c r="O20">
+        <v>0.2169963161816962</v>
+      </c>
+      <c r="P20">
+        <v>0.9396910838183039</v>
+      </c>
+      <c r="Q20">
+        <v>2.159691083818304</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1133897149893582</v>
+      </c>
+      <c r="T20">
+        <v>0.6566574607788773</v>
+      </c>
+      <c r="U20">
+        <v>0.0609</v>
+      </c>
+      <c r="V20">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W20">
+        <v>0.04947506733844832</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>3.017550983529753</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.1040340551432529</v>
+      </c>
+      <c r="C21">
+        <v>42.85448455860499</v>
+      </c>
+      <c r="D21">
+        <v>48.18148455860499</v>
+      </c>
+      <c r="E21">
+        <v>-13.263</v>
+      </c>
+      <c r="F21">
+        <v>9.936999999999999</v>
+      </c>
+      <c r="G21">
+        <v>4.61</v>
+      </c>
+      <c r="H21">
+        <v>29.1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>2.95</v>
+      </c>
+      <c r="K21">
+        <v>1.22</v>
+      </c>
+      <c r="L21">
+        <v>1.73</v>
+      </c>
+      <c r="M21">
+        <v>0.7442812999999999</v>
+      </c>
+      <c r="N21">
+        <v>0.9857187000000001</v>
+      </c>
+      <c r="O21">
+        <v>0.1849223279266382</v>
+      </c>
+      <c r="P21">
+        <v>0.8007963720733619</v>
+      </c>
+      <c r="Q21">
+        <v>2.020796372073362</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1141639659212764</v>
+      </c>
+      <c r="T21">
+        <v>0.6634736505314678</v>
+      </c>
+      <c r="U21">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V21">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W21">
+        <v>0.06084864603694218</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>2.324389985345594</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.1041357877085825</v>
+      </c>
+      <c r="C22">
+        <v>42.25646248881073</v>
+      </c>
+      <c r="D22">
+        <v>48.10646248881073</v>
+      </c>
+      <c r="E22">
+        <v>-12.74</v>
+      </c>
+      <c r="F22">
+        <v>10.46</v>
+      </c>
+      <c r="G22">
+        <v>4.61</v>
+      </c>
+      <c r="H22">
+        <v>29.1</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>2.95</v>
+      </c>
+      <c r="K22">
+        <v>1.22</v>
+      </c>
+      <c r="L22">
+        <v>1.73</v>
+      </c>
+      <c r="M22">
+        <v>0.783454</v>
+      </c>
+      <c r="N22">
+        <v>0.946546</v>
+      </c>
+      <c r="O22">
+        <v>0.1775734698039589</v>
+      </c>
+      <c r="P22">
+        <v>0.7689725301960411</v>
+      </c>
+      <c r="Q22">
+        <v>1.988972530196041</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1149575731264926</v>
+      </c>
+      <c r="T22">
+        <v>0.6704602450278732</v>
+      </c>
+      <c r="U22">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V22">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W22">
+        <v>0.06084864603694218</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>2.208170486078314</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.1042375202739121</v>
+      </c>
+      <c r="C23">
+        <v>41.65867368542342</v>
+      </c>
+      <c r="D23">
+        <v>48.03167368542341</v>
+      </c>
+      <c r="E23">
+        <v>-12.217</v>
+      </c>
+      <c r="F23">
+        <v>10.983</v>
+      </c>
+      <c r="G23">
+        <v>4.61</v>
+      </c>
+      <c r="H23">
+        <v>29.1</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>2.95</v>
+      </c>
+      <c r="K23">
+        <v>1.22</v>
+      </c>
+      <c r="L23">
+        <v>1.73</v>
+      </c>
+      <c r="M23">
+        <v>0.8226266999999998</v>
+      </c>
+      <c r="N23">
+        <v>0.9073733000000002</v>
+      </c>
+      <c r="O23">
+        <v>0.1702246116812797</v>
+      </c>
+      <c r="P23">
+        <v>0.7371486883187204</v>
+      </c>
+      <c r="Q23">
+        <v>1.957148688318721</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1157712716533598</v>
+      </c>
+      <c r="T23">
+        <v>0.6776237153343139</v>
+      </c>
+      <c r="U23">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V23">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W23">
+        <v>0.06084864603694218</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>2.103019510550777</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.1043392528392418</v>
+      </c>
+      <c r="C24">
+        <v>41.06111706218758</v>
+      </c>
+      <c r="D24">
+        <v>47.95711706218759</v>
+      </c>
+      <c r="E24">
+        <v>-11.694</v>
+      </c>
+      <c r="F24">
+        <v>11.506</v>
+      </c>
+      <c r="G24">
+        <v>4.61</v>
+      </c>
+      <c r="H24">
+        <v>29.1</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>2.95</v>
+      </c>
+      <c r="K24">
+        <v>1.22</v>
+      </c>
+      <c r="L24">
+        <v>1.73</v>
+      </c>
+      <c r="M24">
+        <v>0.8617994</v>
+      </c>
+      <c r="N24">
+        <v>0.8682006</v>
+      </c>
+      <c r="O24">
+        <v>0.1628757535586005</v>
+      </c>
+      <c r="P24">
+        <v>0.7053248464413995</v>
+      </c>
+      <c r="Q24">
+        <v>1.9253248464414</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1166058342450186</v>
+      </c>
+      <c r="T24">
+        <v>0.684970864366561</v>
+      </c>
+      <c r="U24">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V24">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W24">
+        <v>0.06084864603694218</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>2.00742771461665</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.1074866673003324</v>
+      </c>
+      <c r="C25">
+        <v>38.34058834684382</v>
+      </c>
+      <c r="D25">
+        <v>45.75958834684382</v>
+      </c>
+      <c r="E25">
+        <v>-11.171</v>
+      </c>
+      <c r="F25">
+        <v>12.029</v>
+      </c>
+      <c r="G25">
+        <v>4.61</v>
+      </c>
+      <c r="H25">
+        <v>29.1</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>2.95</v>
+      </c>
+      <c r="K25">
+        <v>1.22</v>
+      </c>
+      <c r="L25">
+        <v>1.73</v>
+      </c>
+      <c r="M25">
+        <v>1.0970448</v>
+      </c>
+      <c r="N25">
+        <v>0.6329552000000001</v>
+      </c>
+      <c r="O25">
+        <v>0.1187433585842197</v>
+      </c>
+      <c r="P25">
+        <v>0.5142118414157804</v>
+      </c>
+      <c r="Q25">
+        <v>1.734211841415781</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.11746207378711</v>
+      </c>
+      <c r="T25">
+        <v>0.6925088484386066</v>
+      </c>
+      <c r="U25">
+        <v>0.0912</v>
+      </c>
+      <c r="V25">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W25">
+        <v>0.07409074123590291</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>1.576963857811459</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.1077208208176516</v>
+      </c>
+      <c r="C26">
+        <v>37.66212344617409</v>
+      </c>
+      <c r="D26">
+        <v>45.60412344617409</v>
+      </c>
+      <c r="E26">
+        <v>-10.648</v>
+      </c>
+      <c r="F26">
+        <v>12.552</v>
+      </c>
+      <c r="G26">
+        <v>4.61</v>
+      </c>
+      <c r="H26">
+        <v>29.1</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2.95</v>
+      </c>
+      <c r="K26">
+        <v>1.22</v>
+      </c>
+      <c r="L26">
+        <v>1.73</v>
+      </c>
+      <c r="M26">
+        <v>1.1447424</v>
+      </c>
+      <c r="N26">
+        <v>0.5852576</v>
+      </c>
+      <c r="O26">
+        <v>0.1097952162505969</v>
+      </c>
+      <c r="P26">
+        <v>0.4754623837494031</v>
+      </c>
+      <c r="Q26">
+        <v>1.695462383749403</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1183408459487301</v>
+      </c>
+      <c r="T26">
+        <v>0.7002452005125481</v>
+      </c>
+      <c r="U26">
+        <v>0.0912</v>
+      </c>
+      <c r="V26">
+        <v>0.1876015215361524</v>
+      </c>
+      <c r="W26">
+        <v>0.07409074123590291</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>1.511257030402648</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.12283715785043</v>
+      </c>
+      <c r="C27">
+        <v>28.93599856986948</v>
+      </c>
+      <c r="D27">
+        <v>37.40099856986948</v>
+      </c>
+      <c r="E27">
+        <v>-10.125</v>
+      </c>
+      <c r="F27">
+        <v>13.075</v>
+      </c>
+      <c r="G27">
+        <v>4.61</v>
+      </c>
+      <c r="H27">
+        <v>29.1</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>2.95</v>
+      </c>
+      <c r="K27">
+        <v>1.22</v>
+      </c>
+      <c r="L27">
+        <v>1.73</v>
+      </c>
+      <c r="M27">
+        <v>2.047545</v>
+      </c>
+      <c r="N27">
+        <v>-0.317545</v>
+      </c>
+      <c r="O27">
+        <v>-0.05957192515619751</v>
+      </c>
+      <c r="P27">
+        <v>-0.2579730748438024</v>
+      </c>
+      <c r="Q27">
+        <v>0.9620269251561977</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.119856953163417</v>
+      </c>
+      <c r="T27">
+        <v>0.7135923907251246</v>
+      </c>
+      <c r="U27">
+        <v>0.1566</v>
+      </c>
+      <c r="V27">
+        <v>0.1585072036304666</v>
+      </c>
+      <c r="W27">
+        <v>0.1317777719114689</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>0.844914275388331</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.12401515785043</v>
+      </c>
+      <c r="C28">
+        <v>27.89597346040905</v>
+      </c>
+      <c r="D28">
+        <v>36.88397346040905</v>
+      </c>
+      <c r="E28">
+        <v>-9.602</v>
+      </c>
+      <c r="F28">
+        <v>13.598</v>
+      </c>
+      <c r="G28">
+        <v>4.61</v>
+      </c>
+      <c r="H28">
+        <v>29.1</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>2.95</v>
+      </c>
+      <c r="K28">
+        <v>1.22</v>
+      </c>
+      <c r="L28">
+        <v>1.73</v>
+      </c>
+      <c r="M28">
+        <v>2.1294468</v>
+      </c>
+      <c r="N28">
+        <v>-0.3994468000000002</v>
+      </c>
+      <c r="O28">
+        <v>-0.07493682745274721</v>
+      </c>
+      <c r="P28">
+        <v>-0.324509972547253</v>
+      </c>
+      <c r="Q28">
+        <v>0.8954900274527472</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.120952317395355</v>
+      </c>
+      <c r="T28">
+        <v>0.723235531140329</v>
+      </c>
+      <c r="U28">
+        <v>0.1566</v>
+      </c>
+      <c r="V28">
+        <v>0.1524107727216025</v>
+      </c>
+      <c r="W28">
+        <v>0.1327324729917971</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>0.8124175724887797</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.1399142632327869</v>
+      </c>
+      <c r="C29">
+        <v>21.57337445015836</v>
+      </c>
+      <c r="D29">
+        <v>31.08437445015836</v>
+      </c>
+      <c r="E29">
+        <v>-9.078999999999999</v>
+      </c>
+      <c r="F29">
+        <v>14.121</v>
+      </c>
+      <c r="G29">
+        <v>4.61</v>
+      </c>
+      <c r="H29">
+        <v>29.1</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>2.95</v>
+      </c>
+      <c r="K29">
+        <v>1.22</v>
+      </c>
+      <c r="L29">
+        <v>1.73</v>
+      </c>
+      <c r="M29">
+        <v>2.9484648</v>
+      </c>
+      <c r="N29">
+        <v>-1.2184648</v>
+      </c>
+      <c r="O29">
+        <v>-0.2285858504182438</v>
+      </c>
+      <c r="P29">
+        <v>-0.9898789495817567</v>
+      </c>
+      <c r="Q29">
+        <v>0.2301210504182435</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1229367400752324</v>
+      </c>
+      <c r="T29">
+        <v>0.7407055799033008</v>
+      </c>
+      <c r="U29">
+        <v>0.2088</v>
+      </c>
+      <c r="V29">
+        <v>0.1100744469656018</v>
+      </c>
+      <c r="W29">
+        <v>0.1858164554735824</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>0.5867460245752296</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.1416142632327869</v>
+      </c>
+      <c r="C30">
+        <v>20.53640455042156</v>
+      </c>
+      <c r="D30">
+        <v>30.57040455042155</v>
+      </c>
+      <c r="E30">
+        <v>-8.555999999999999</v>
+      </c>
+      <c r="F30">
+        <v>14.644</v>
+      </c>
+      <c r="G30">
+        <v>4.61</v>
+      </c>
+      <c r="H30">
+        <v>29.1</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>2.95</v>
+      </c>
+      <c r="K30">
+        <v>1.22</v>
+      </c>
+      <c r="L30">
+        <v>1.73</v>
+      </c>
+      <c r="M30">
+        <v>3.0576672</v>
+      </c>
+      <c r="N30">
+        <v>-1.3276672</v>
+      </c>
+      <c r="O30">
+        <v>-0.2490723868136432</v>
+      </c>
+      <c r="P30">
+        <v>-1.078594813186357</v>
+      </c>
+      <c r="Q30">
+        <v>0.1414051868136434</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1241053059096106</v>
+      </c>
+      <c r="T30">
+        <v>0.7509931574019577</v>
+      </c>
+      <c r="U30">
+        <v>0.2088</v>
+      </c>
+      <c r="V30">
+        <v>0.1061432167168303</v>
+      </c>
+      <c r="W30">
+        <v>0.1866372963495259</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>0.5657908094118287</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.1433142632327868</v>
+      </c>
+      <c r="C31">
+        <v>19.51615483417985</v>
+      </c>
+      <c r="D31">
+        <v>30.07315483417984</v>
+      </c>
+      <c r="E31">
+        <v>-8.033000000000001</v>
+      </c>
+      <c r="F31">
+        <v>15.167</v>
+      </c>
+      <c r="G31">
+        <v>4.61</v>
+      </c>
+      <c r="H31">
+        <v>29.1</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2.95</v>
+      </c>
+      <c r="K31">
+        <v>1.22</v>
+      </c>
+      <c r="L31">
+        <v>1.73</v>
+      </c>
+      <c r="M31">
+        <v>3.1668696</v>
+      </c>
+      <c r="N31">
+        <v>-1.4368696</v>
+      </c>
+      <c r="O31">
+        <v>-0.2695589232090426</v>
+      </c>
+      <c r="P31">
+        <v>-1.167310676790957</v>
+      </c>
+      <c r="Q31">
+        <v>0.05268932320904307</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1253067890914361</v>
+      </c>
+      <c r="T31">
+        <v>0.7615705258160698</v>
+      </c>
+      <c r="U31">
+        <v>0.2088</v>
+      </c>
+      <c r="V31">
+        <v>0.1024831057955603</v>
+      </c>
+      <c r="W31">
+        <v>0.187401527509887</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>0.5462807815010761</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.1450142632327868</v>
+      </c>
+      <c r="C32">
+        <v>18.51182246259376</v>
+      </c>
+      <c r="D32">
+        <v>29.59182246259375</v>
+      </c>
+      <c r="E32">
+        <v>-7.510000000000002</v>
+      </c>
+      <c r="F32">
+        <v>15.69</v>
+      </c>
+      <c r="G32">
+        <v>4.61</v>
+      </c>
+      <c r="H32">
+        <v>29.1</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2.95</v>
+      </c>
+      <c r="K32">
+        <v>1.22</v>
+      </c>
+      <c r="L32">
+        <v>1.73</v>
+      </c>
+      <c r="M32">
+        <v>3.276072</v>
+      </c>
+      <c r="N32">
+        <v>-1.546072</v>
+      </c>
+      <c r="O32">
+        <v>-0.2900454596044422</v>
+      </c>
+      <c r="P32">
+        <v>-1.256026540395558</v>
+      </c>
+      <c r="Q32">
+        <v>-0.0360265403955573</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1265426003641709</v>
+      </c>
+      <c r="T32">
+        <v>0.7724501047562994</v>
+      </c>
+      <c r="U32">
+        <v>0.2088</v>
+      </c>
+      <c r="V32">
+        <v>0.09906700226904162</v>
+      </c>
+      <c r="W32">
+        <v>0.1881148099262241</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>0.5280714221177069</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.1467142632327868</v>
+      </c>
+      <c r="C33">
+        <v>17.52265518609675</v>
+      </c>
+      <c r="D33">
+        <v>29.12565518609674</v>
+      </c>
+      <c r="E33">
+        <v>-6.987000000000002</v>
+      </c>
+      <c r="F33">
+        <v>16.213</v>
+      </c>
+      <c r="G33">
+        <v>4.61</v>
+      </c>
+      <c r="H33">
+        <v>29.1</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>2.95</v>
+      </c>
+      <c r="K33">
+        <v>1.22</v>
+      </c>
+      <c r="L33">
+        <v>1.73</v>
+      </c>
+      <c r="M33">
+        <v>3.3852744</v>
+      </c>
+      <c r="N33">
+        <v>-1.6552744</v>
+      </c>
+      <c r="O33">
+        <v>-0.3105319959998417</v>
+      </c>
+      <c r="P33">
+        <v>-1.344742404000158</v>
+      </c>
+      <c r="Q33">
+        <v>-0.1247424040001577</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1278142322535067</v>
+      </c>
+      <c r="T33">
+        <v>0.7836450338107385</v>
+      </c>
+      <c r="U33">
+        <v>0.2088</v>
+      </c>
+      <c r="V33">
+        <v>0.09587129251842737</v>
+      </c>
+      <c r="W33">
+        <v>0.1887820741221524</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>0.5110368601139099</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.1582506094824188</v>
+      </c>
+      <c r="C34">
+        <v>14.18674661719023</v>
+      </c>
+      <c r="D34">
+        <v>26.31274661719023</v>
+      </c>
+      <c r="E34">
+        <v>-6.463999999999999</v>
+      </c>
+      <c r="F34">
+        <v>16.736</v>
+      </c>
+      <c r="G34">
+        <v>4.61</v>
+      </c>
+      <c r="H34">
+        <v>29.1</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>2.95</v>
+      </c>
+      <c r="K34">
+        <v>1.22</v>
+      </c>
+      <c r="L34">
+        <v>1.73</v>
+      </c>
+      <c r="M34">
+        <v>3.9965568</v>
+      </c>
+      <c r="N34">
+        <v>-2.2665568</v>
+      </c>
+      <c r="O34">
+        <v>-0.4252095043281128</v>
+      </c>
+      <c r="P34">
+        <v>-1.841347295671888</v>
+      </c>
+      <c r="Q34">
+        <v>-0.6213472956718875</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1294708330949288</v>
+      </c>
+      <c r="T34">
+        <v>0.7982290726719624</v>
+      </c>
+      <c r="U34">
+        <v>0.2388</v>
+      </c>
+      <c r="V34">
+        <v>0.08120756153335382</v>
+      </c>
+      <c r="W34">
+        <v>0.2194076343058351</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>0.4328726167484971</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.1602506094824188</v>
+      </c>
+      <c r="C35">
+        <v>13.23043884328401</v>
+      </c>
+      <c r="D35">
+        <v>25.87943884328401</v>
+      </c>
+      <c r="E35">
+        <v>-5.940999999999999</v>
+      </c>
+      <c r="F35">
+        <v>17.259</v>
+      </c>
+      <c r="G35">
+        <v>4.61</v>
+      </c>
+      <c r="H35">
+        <v>29.1</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>2.95</v>
+      </c>
+      <c r="K35">
+        <v>1.22</v>
+      </c>
+      <c r="L35">
+        <v>1.73</v>
+      </c>
+      <c r="M35">
+        <v>4.121449200000001</v>
+      </c>
+      <c r="N35">
+        <v>-2.391449200000001</v>
+      </c>
+      <c r="O35">
+        <v>-0.4486395085964146</v>
+      </c>
+      <c r="P35">
+        <v>-1.942809691403586</v>
+      </c>
+      <c r="Q35">
+        <v>-0.722809691403586</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.1308241291112711</v>
+      </c>
+      <c r="T35">
+        <v>0.8101429394282603</v>
+      </c>
+      <c r="U35">
+        <v>0.2388</v>
+      </c>
+      <c r="V35">
+        <v>0.0787467263353734</v>
+      </c>
+      <c r="W35">
+        <v>0.2199952817511129</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>0.4197552647258153</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.1622506094824188</v>
+      </c>
+      <c r="C36">
+        <v>12.2881709441333</v>
+      </c>
+      <c r="D36">
+        <v>25.4601709441333</v>
+      </c>
+      <c r="E36">
+        <v>-5.417999999999999</v>
+      </c>
+      <c r="F36">
+        <v>17.782</v>
+      </c>
+      <c r="G36">
+        <v>4.61</v>
+      </c>
+      <c r="H36">
+        <v>29.1</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>2.95</v>
+      </c>
+      <c r="K36">
+        <v>1.22</v>
+      </c>
+      <c r="L36">
+        <v>1.73</v>
+      </c>
+      <c r="M36">
+        <v>4.2463416</v>
+      </c>
+      <c r="N36">
+        <v>-2.5163416</v>
+      </c>
+      <c r="O36">
+        <v>-0.4720695128647163</v>
+      </c>
+      <c r="P36">
+        <v>-2.044272087135284</v>
+      </c>
+      <c r="Q36">
+        <v>-0.8242720871352835</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1322184340978055</v>
+      </c>
+      <c r="T36">
+        <v>0.8224178324499006</v>
+      </c>
+      <c r="U36">
+        <v>0.2388</v>
+      </c>
+      <c r="V36">
+        <v>0.0764306461490389</v>
+      </c>
+      <c r="W36">
+        <v>0.2205483616996095</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>0.4074095216456444</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.1642506094824188</v>
+      </c>
+      <c r="C37">
+        <v>11.35927142639997</v>
+      </c>
+      <c r="D37">
+        <v>25.05427142639997</v>
+      </c>
+      <c r="E37">
+        <v>-4.895</v>
+      </c>
+      <c r="F37">
+        <v>18.305</v>
+      </c>
+      <c r="G37">
+        <v>4.61</v>
+      </c>
+      <c r="H37">
+        <v>29.1</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2.95</v>
+      </c>
+      <c r="K37">
+        <v>1.22</v>
+      </c>
+      <c r="L37">
+        <v>1.73</v>
+      </c>
+      <c r="M37">
+        <v>4.371234</v>
+      </c>
+      <c r="N37">
+        <v>-2.641234</v>
+      </c>
+      <c r="O37">
+        <v>-0.495499517133018</v>
+      </c>
+      <c r="P37">
+        <v>-2.145734482866982</v>
+      </c>
+      <c r="Q37">
+        <v>-0.9257344828669822</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1336556407762332</v>
+      </c>
+      <c r="T37">
+        <v>0.8350704144875915</v>
+      </c>
+      <c r="U37">
+        <v>0.2388</v>
+      </c>
+      <c r="V37">
+        <v>0.07424691340192351</v>
+      </c>
+      <c r="W37">
+        <v>0.2210698370796207</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>0.3957692495986259</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.1662506094824188</v>
+      </c>
+      <c r="C38">
+        <v>10.44311094598883</v>
+      </c>
+      <c r="D38">
+        <v>24.66111094598883</v>
+      </c>
+      <c r="E38">
+        <v>-4.372</v>
+      </c>
+      <c r="F38">
+        <v>18.828</v>
+      </c>
+      <c r="G38">
+        <v>4.61</v>
+      </c>
+      <c r="H38">
+        <v>29.1</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>2.95</v>
+      </c>
+      <c r="K38">
+        <v>1.22</v>
+      </c>
+      <c r="L38">
+        <v>1.73</v>
+      </c>
+      <c r="M38">
+        <v>4.496126400000001</v>
+      </c>
+      <c r="N38">
+        <v>-2.766126400000001</v>
+      </c>
+      <c r="O38">
+        <v>-0.5189295214013199</v>
+      </c>
+      <c r="P38">
+        <v>-2.247196878598681</v>
+      </c>
+      <c r="Q38">
+        <v>-1.02719687859868</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1351377601633619</v>
+      </c>
+      <c r="T38">
+        <v>0.84811838971396</v>
+      </c>
+      <c r="U38">
+        <v>0.2388</v>
+      </c>
+      <c r="V38">
+        <v>0.07218449914075895</v>
+      </c>
+      <c r="W38">
+        <v>0.2215623416051868</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>0.3847756593319974</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.1682506094824188</v>
+      </c>
+      <c r="C39">
+        <v>9.539099052038061</v>
+      </c>
+      <c r="D39">
+        <v>24.28009905203806</v>
+      </c>
+      <c r="E39">
+        <v>-3.849</v>
+      </c>
+      <c r="F39">
+        <v>19.351</v>
+      </c>
+      <c r="G39">
+        <v>4.61</v>
+      </c>
+      <c r="H39">
+        <v>29.1</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2.95</v>
+      </c>
+      <c r="K39">
+        <v>1.22</v>
+      </c>
+      <c r="L39">
+        <v>1.73</v>
+      </c>
+      <c r="M39">
+        <v>4.6210188</v>
+      </c>
+      <c r="N39">
+        <v>-2.8910188</v>
+      </c>
+      <c r="O39">
+        <v>-0.5423595256696215</v>
+      </c>
+      <c r="P39">
+        <v>-2.348659274330378</v>
+      </c>
+      <c r="Q39">
+        <v>-1.128659274330378</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1366669309596057</v>
+      </c>
+      <c r="T39">
+        <v>0.8615805863760865</v>
+      </c>
+      <c r="U39">
+        <v>0.2388</v>
+      </c>
+      <c r="V39">
+        <v>0.07023356673154926</v>
+      </c>
+      <c r="W39">
+        <v>0.2220282242645061</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>0.3743763171878894</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.1702506094824189</v>
+      </c>
+      <c r="C40">
+        <v>8.64668122814755</v>
+      </c>
+      <c r="D40">
+        <v>23.91068122814755</v>
+      </c>
+      <c r="E40">
+        <v>-3.326000000000001</v>
+      </c>
+      <c r="F40">
+        <v>19.874</v>
+      </c>
+      <c r="G40">
+        <v>4.61</v>
+      </c>
+      <c r="H40">
+        <v>29.1</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>2.95</v>
+      </c>
+      <c r="K40">
+        <v>1.22</v>
+      </c>
+      <c r="L40">
+        <v>1.73</v>
+      </c>
+      <c r="M40">
+        <v>4.7459112</v>
+      </c>
+      <c r="N40">
+        <v>-3.0159112</v>
+      </c>
+      <c r="O40">
+        <v>-0.5657895299379233</v>
+      </c>
+      <c r="P40">
+        <v>-2.450121670062077</v>
+      </c>
+      <c r="Q40">
+        <v>-1.230121670062077</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.138245429846051</v>
+      </c>
+      <c r="T40">
+        <v>0.8754770474466684</v>
+      </c>
+      <c r="U40">
+        <v>0.2388</v>
+      </c>
+      <c r="V40">
+        <v>0.06838531497545586</v>
+      </c>
+      <c r="W40">
+        <v>0.2224695867838611</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>0.3645243088408396</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.1722506094824188</v>
+      </c>
+      <c r="C41">
+        <v>7.765336199662727</v>
+      </c>
+      <c r="D41">
+        <v>23.55233619966273</v>
+      </c>
+      <c r="E41">
+        <v>-2.803000000000001</v>
+      </c>
+      <c r="F41">
+        <v>20.397</v>
+      </c>
+      <c r="G41">
+        <v>4.61</v>
+      </c>
+      <c r="H41">
+        <v>29.1</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2.95</v>
+      </c>
+      <c r="K41">
+        <v>1.22</v>
+      </c>
+      <c r="L41">
+        <v>1.73</v>
+      </c>
+      <c r="M41">
+        <v>4.870803599999999</v>
+      </c>
+      <c r="N41">
+        <v>-3.140803599999999</v>
+      </c>
+      <c r="O41">
+        <v>-0.589219534206225</v>
+      </c>
+      <c r="P41">
+        <v>-2.551584065793775</v>
+      </c>
+      <c r="Q41">
+        <v>-1.331584065793774</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1398756827943469</v>
+      </c>
+      <c r="T41">
+        <v>0.8898291301916958</v>
+      </c>
+      <c r="U41">
+        <v>0.2388</v>
+      </c>
+      <c r="V41">
+        <v>0.06663184536070059</v>
+      </c>
+      <c r="W41">
+        <v>0.2228883153278647</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>0.3551775316910746</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.1742506094824188</v>
+      </c>
+      <c r="C42">
+        <v>6.894573479514612</v>
+      </c>
+      <c r="D42">
+        <v>23.20457347951461</v>
+      </c>
+      <c r="E42">
+        <v>-2.279999999999998</v>
+      </c>
+      <c r="F42">
+        <v>20.92</v>
+      </c>
+      <c r="G42">
+        <v>4.61</v>
+      </c>
+      <c r="H42">
+        <v>29.1</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>2.95</v>
+      </c>
+      <c r="K42">
+        <v>1.22</v>
+      </c>
+      <c r="L42">
+        <v>1.73</v>
+      </c>
+      <c r="M42">
+        <v>4.995696000000001</v>
+      </c>
+      <c r="N42">
+        <v>-3.265696000000001</v>
+      </c>
+      <c r="O42">
+        <v>-0.612649538474527</v>
+      </c>
+      <c r="P42">
+        <v>-2.653046461525474</v>
+      </c>
+      <c r="Q42">
+        <v>-1.433046461525473</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.141560277507586</v>
+      </c>
+      <c r="T42">
+        <v>0.9046596156948907</v>
+      </c>
+      <c r="U42">
+        <v>0.2388</v>
+      </c>
+      <c r="V42">
+        <v>0.06496604922668306</v>
+      </c>
+      <c r="W42">
+        <v>0.2232861074446681</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>0.3462980933987977</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.1762506094824189</v>
+      </c>
+      <c r="C43">
+        <v>6.033931128318155</v>
+      </c>
+      <c r="D43">
+        <v>22.86693112831816</v>
+      </c>
+      <c r="E43">
+        <v>-1.756999999999998</v>
+      </c>
+      <c r="F43">
+        <v>21.443</v>
+      </c>
+      <c r="G43">
+        <v>4.61</v>
+      </c>
+      <c r="H43">
+        <v>29.1</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>2.95</v>
+      </c>
+      <c r="K43">
+        <v>1.22</v>
+      </c>
+      <c r="L43">
+        <v>1.73</v>
+      </c>
+      <c r="M43">
+        <v>5.120588400000001</v>
+      </c>
+      <c r="N43">
+        <v>-3.390588400000001</v>
+      </c>
+      <c r="O43">
+        <v>-0.6360795427428287</v>
+      </c>
+      <c r="P43">
+        <v>-2.754508857257172</v>
+      </c>
+      <c r="Q43">
+        <v>-1.534508857257172</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1433019771263587</v>
+      </c>
+      <c r="T43">
+        <v>0.9199928295202279</v>
+      </c>
+      <c r="U43">
+        <v>0.2388</v>
+      </c>
+      <c r="V43">
+        <v>0.06338151144066639</v>
+      </c>
+      <c r="W43">
+        <v>0.2236644950679689</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>0.3378517984378513</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.1782506094824189</v>
+      </c>
+      <c r="C44">
+        <v>5.182973707218451</v>
+      </c>
+      <c r="D44">
+        <v>22.53897370721845</v>
+      </c>
+      <c r="E44">
+        <v>-1.234000000000002</v>
+      </c>
+      <c r="F44">
+        <v>21.966</v>
+      </c>
+      <c r="G44">
+        <v>4.61</v>
+      </c>
+      <c r="H44">
+        <v>29.1</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>2.95</v>
+      </c>
+      <c r="K44">
+        <v>1.22</v>
+      </c>
+      <c r="L44">
+        <v>1.73</v>
+      </c>
+      <c r="M44">
+        <v>5.245480799999999</v>
+      </c>
+      <c r="N44">
+        <v>-3.515480799999999</v>
+      </c>
+      <c r="O44">
+        <v>-0.6595095470111302</v>
+      </c>
+      <c r="P44">
+        <v>-2.855971252988869</v>
+      </c>
+      <c r="Q44">
+        <v>-1.635971252988869</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1451037353526752</v>
+      </c>
+      <c r="T44">
+        <v>0.9358547748567834</v>
+      </c>
+      <c r="U44">
+        <v>0.2388</v>
+      </c>
+      <c r="V44">
+        <v>0.06187242783493627</v>
+      </c>
+      <c r="W44">
+        <v>0.2240248642330172</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>0.3298077079988549</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.1802506094824189</v>
+      </c>
+      <c r="C45">
+        <v>4.3412904044078</v>
+      </c>
+      <c r="D45">
+        <v>22.2202904044078</v>
+      </c>
+      <c r="E45">
+        <v>-0.7110000000000021</v>
+      </c>
+      <c r="F45">
+        <v>22.489</v>
+      </c>
+      <c r="G45">
+        <v>4.61</v>
+      </c>
+      <c r="H45">
+        <v>29.1</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>2.95</v>
+      </c>
+      <c r="K45">
+        <v>1.22</v>
+      </c>
+      <c r="L45">
+        <v>1.73</v>
+      </c>
+      <c r="M45">
+        <v>5.3703732</v>
+      </c>
+      <c r="N45">
+        <v>-3.6403732</v>
+      </c>
+      <c r="O45">
+        <v>-0.6829395512794321</v>
+      </c>
+      <c r="P45">
+        <v>-2.957433648720567</v>
+      </c>
+      <c r="Q45">
+        <v>-1.737433648720567</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.14696871316588</v>
+      </c>
+      <c r="T45">
+        <v>0.9522732796788324</v>
+      </c>
+      <c r="U45">
+        <v>0.2388</v>
+      </c>
+      <c r="V45">
+        <v>0.06043353416435635</v>
+      </c>
+      <c r="W45">
+        <v>0.2243684720415517</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>0.3221377613012072</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.1822506094824189</v>
+      </c>
+      <c r="C46">
+        <v>3.508493318364312</v>
+      </c>
+      <c r="D46">
+        <v>21.91049331836431</v>
+      </c>
+      <c r="E46">
+        <v>-0.1879999999999988</v>
+      </c>
+      <c r="F46">
+        <v>23.012</v>
+      </c>
+      <c r="G46">
+        <v>4.61</v>
+      </c>
+      <c r="H46">
+        <v>29.1</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>2.95</v>
+      </c>
+      <c r="K46">
+        <v>1.22</v>
+      </c>
+      <c r="L46">
+        <v>1.73</v>
+      </c>
+      <c r="M46">
+        <v>5.495265600000001</v>
+      </c>
+      <c r="N46">
+        <v>-3.765265600000001</v>
+      </c>
+      <c r="O46">
+        <v>-0.706369555547734</v>
+      </c>
+      <c r="P46">
+        <v>-3.058896044452267</v>
+      </c>
+      <c r="Q46">
+        <v>-1.838896044452266</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.1489002973295565</v>
+      </c>
+      <c r="T46">
+        <v>0.9692781596730973</v>
+      </c>
+      <c r="U46">
+        <v>0.2388</v>
+      </c>
+      <c r="V46">
+        <v>0.05906004475153005</v>
+      </c>
+      <c r="W46">
+        <v>0.2246964613133347</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>0.3148164485443615</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.1842506094824188</v>
+      </c>
+      <c r="C47">
+        <v>2.684215882727134</v>
+      </c>
+      <c r="D47">
+        <v>21.60921588272713</v>
+      </c>
+      <c r="E47">
+        <v>0.3350000000000009</v>
+      </c>
+      <c r="F47">
+        <v>23.535</v>
+      </c>
+      <c r="G47">
+        <v>4.61</v>
+      </c>
+      <c r="H47">
+        <v>29.1</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>2.95</v>
+      </c>
+      <c r="K47">
+        <v>1.22</v>
+      </c>
+      <c r="L47">
+        <v>1.73</v>
+      </c>
+      <c r="M47">
+        <v>5.620158</v>
+      </c>
+      <c r="N47">
+        <v>-3.890158</v>
+      </c>
+      <c r="O47">
+        <v>-0.7297995598160356</v>
+      </c>
+      <c r="P47">
+        <v>-3.160358440183964</v>
+      </c>
+      <c r="Q47">
+        <v>-1.940358440183964</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1509021209173665</v>
+      </c>
+      <c r="T47">
+        <v>0.9869013989398807</v>
+      </c>
+      <c r="U47">
+        <v>0.2388</v>
+      </c>
+      <c r="V47">
+        <v>0.05774759931260717</v>
+      </c>
+      <c r="W47">
+        <v>0.2250098732841494</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>0.307820527465598</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1862506094824188</v>
+      </c>
+      <c r="C48">
+        <v>1.868111419360318</v>
+      </c>
+      <c r="D48">
+        <v>21.31611141936032</v>
+      </c>
+      <c r="E48">
+        <v>0.8580000000000005</v>
+      </c>
+      <c r="F48">
+        <v>24.058</v>
+      </c>
+      <c r="G48">
+        <v>4.61</v>
+      </c>
+      <c r="H48">
+        <v>29.1</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>2.95</v>
+      </c>
+      <c r="K48">
+        <v>1.22</v>
+      </c>
+      <c r="L48">
+        <v>1.73</v>
+      </c>
+      <c r="M48">
+        <v>5.7450504</v>
+      </c>
+      <c r="N48">
+        <v>-4.0150504</v>
+      </c>
+      <c r="O48">
+        <v>-0.7532295640843374</v>
+      </c>
+      <c r="P48">
+        <v>-3.261820835915662</v>
+      </c>
+      <c r="Q48">
+        <v>-2.041820835915662</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.15297808611954</v>
+      </c>
+      <c r="T48">
+        <v>1.005177350772101</v>
+      </c>
+      <c r="U48">
+        <v>0.2388</v>
+      </c>
+      <c r="V48">
+        <v>0.05649221671885483</v>
+      </c>
+      <c r="W48">
+        <v>0.2253096586475375</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>0.3011287768685198</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.1882506094824188</v>
+      </c>
+      <c r="C49">
+        <v>1.05985180759717</v>
+      </c>
+      <c r="D49">
+        <v>21.03085180759717</v>
+      </c>
+      <c r="E49">
+        <v>1.381</v>
+      </c>
+      <c r="F49">
+        <v>24.581</v>
+      </c>
+      <c r="G49">
+        <v>4.61</v>
+      </c>
+      <c r="H49">
+        <v>29.1</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>2.95</v>
+      </c>
+      <c r="K49">
+        <v>1.22</v>
+      </c>
+      <c r="L49">
+        <v>1.73</v>
+      </c>
+      <c r="M49">
+        <v>5.8699428</v>
+      </c>
+      <c r="N49">
+        <v>-4.1399428</v>
+      </c>
+      <c r="O49">
+        <v>-0.7766595683526392</v>
+      </c>
+      <c r="P49">
+        <v>-3.363283231647361</v>
+      </c>
+      <c r="Q49">
+        <v>-2.143283231647361</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1551323896312294</v>
+      </c>
+      <c r="T49">
+        <v>1.024142961164027</v>
+      </c>
+      <c r="U49">
+        <v>0.2388</v>
+      </c>
+      <c r="V49">
+        <v>0.05529025466100686</v>
+      </c>
+      <c r="W49">
+        <v>0.2255966871869516</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>0.294721781615998</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1902506094824188</v>
+      </c>
+      <c r="C50">
+        <v>0.2591262589252956</v>
+      </c>
+      <c r="D50">
+        <v>20.7531262589253</v>
+      </c>
+      <c r="E50">
+        <v>1.904</v>
+      </c>
+      <c r="F50">
+        <v>25.104</v>
+      </c>
+      <c r="G50">
+        <v>4.61</v>
+      </c>
+      <c r="H50">
+        <v>29.1</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>2.95</v>
+      </c>
+      <c r="K50">
+        <v>1.22</v>
+      </c>
+      <c r="L50">
+        <v>1.73</v>
+      </c>
+      <c r="M50">
+        <v>5.9948352</v>
+      </c>
+      <c r="N50">
+        <v>-4.2648352</v>
+      </c>
+      <c r="O50">
+        <v>-0.8000895726209409</v>
+      </c>
+      <c r="P50">
+        <v>-3.46474562737906</v>
+      </c>
+      <c r="Q50">
+        <v>-2.244745627379059</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1573695509702915</v>
+      </c>
+      <c r="T50">
+        <v>1.043838018109489</v>
+      </c>
+      <c r="U50">
+        <v>0.2388</v>
+      </c>
+      <c r="V50">
+        <v>0.05413837435556923</v>
+      </c>
+      <c r="W50">
+        <v>0.2258717562038901</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>0.288581744498998</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1922506094824188</v>
+      </c>
+      <c r="C51">
+        <v>-0.5343598125073896</v>
+      </c>
+      <c r="D51">
+        <v>20.48264018749261</v>
+      </c>
+      <c r="E51">
+        <v>2.427</v>
+      </c>
+      <c r="F51">
+        <v>25.627</v>
+      </c>
+      <c r="G51">
+        <v>4.61</v>
+      </c>
+      <c r="H51">
+        <v>29.1</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>2.95</v>
+      </c>
+      <c r="K51">
+        <v>1.22</v>
+      </c>
+      <c r="L51">
+        <v>1.73</v>
+      </c>
+      <c r="M51">
+        <v>6.1197276</v>
+      </c>
+      <c r="N51">
+        <v>-4.389727600000001</v>
+      </c>
+      <c r="O51">
+        <v>-0.8235195768892428</v>
+      </c>
+      <c r="P51">
+        <v>-3.566208023110758</v>
+      </c>
+      <c r="Q51">
+        <v>-2.346208023110758</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1596944441265717</v>
+      </c>
+      <c r="T51">
+        <v>1.064305430229283</v>
+      </c>
+      <c r="U51">
+        <v>0.2388</v>
+      </c>
+      <c r="V51">
+        <v>0.0530335095728025</v>
+      </c>
+      <c r="W51">
+        <v>0.2261355979140148</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>0.2826923211418756</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1942506094824188</v>
+      </c>
+      <c r="C52">
+        <v>-1.320885832195451</v>
+      </c>
+      <c r="D52">
+        <v>20.21911416780455</v>
+      </c>
+      <c r="E52">
+        <v>2.949999999999999</v>
+      </c>
+      <c r="F52">
+        <v>26.15</v>
+      </c>
+      <c r="G52">
+        <v>4.61</v>
+      </c>
+      <c r="H52">
+        <v>29.1</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>2.95</v>
+      </c>
+      <c r="K52">
+        <v>1.22</v>
+      </c>
+      <c r="L52">
+        <v>1.73</v>
+      </c>
+      <c r="M52">
+        <v>6.24462</v>
+      </c>
+      <c r="N52">
+        <v>-4.514620000000001</v>
+      </c>
+      <c r="O52">
+        <v>-0.8469495811575446</v>
+      </c>
+      <c r="P52">
+        <v>-3.667670418842456</v>
+      </c>
+      <c r="Q52">
+        <v>-2.447670418842456</v>
+      </c>
+      <c r="R52">
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <v>0.1621123330091032</v>
+      </c>
+      <c r="T52">
+        <v>1.085591538833869</v>
+      </c>
+      <c r="U52">
+        <v>0.2388</v>
+      </c>
+      <c r="V52">
+        <v>0.05197283938134645</v>
+      </c>
+      <c r="W52">
+        <v>0.2263888859557345</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>0.2770384747190381</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1962506094824188</v>
+      </c>
+      <c r="C53">
+        <v>-2.100717028140263</v>
+      </c>
+      <c r="D53">
+        <v>19.96228297185974</v>
+      </c>
+      <c r="E53">
+        <v>3.472999999999999</v>
+      </c>
+      <c r="F53">
+        <v>26.673</v>
+      </c>
+      <c r="G53">
+        <v>4.61</v>
+      </c>
+      <c r="H53">
+        <v>29.1</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>2.95</v>
+      </c>
+      <c r="K53">
+        <v>1.22</v>
+      </c>
+      <c r="L53">
+        <v>1.73</v>
+      </c>
+      <c r="M53">
+        <v>6.3695124</v>
+      </c>
+      <c r="N53">
+        <v>-4.639512399999999</v>
+      </c>
+      <c r="O53">
+        <v>-0.870379585425846</v>
+      </c>
+      <c r="P53">
+        <v>-3.769132814574153</v>
+      </c>
+      <c r="Q53">
+        <v>-2.549132814574153</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1646289112337788</v>
+      </c>
+      <c r="T53">
+        <v>1.107746468197825</v>
+      </c>
+      <c r="U53">
+        <v>0.2388</v>
+      </c>
+      <c r="V53">
+        <v>0.05095376409935927</v>
+      </c>
+      <c r="W53">
+        <v>0.226632241133073</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>0.271606347763763</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1982506094824188</v>
+      </c>
+      <c r="C54">
+        <v>-2.874105321250681</v>
+      </c>
+      <c r="D54">
+        <v>19.71189467874932</v>
+      </c>
+      <c r="E54">
+        <v>3.995999999999999</v>
+      </c>
+      <c r="F54">
+        <v>27.196</v>
+      </c>
+      <c r="G54">
+        <v>4.61</v>
+      </c>
+      <c r="H54">
+        <v>29.1</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>2.95</v>
+      </c>
+      <c r="K54">
+        <v>1.22</v>
+      </c>
+      <c r="L54">
+        <v>1.73</v>
+      </c>
+      <c r="M54">
+        <v>6.4944048</v>
+      </c>
+      <c r="N54">
+        <v>-4.764404799999999</v>
+      </c>
+      <c r="O54">
+        <v>-0.8938095896941478</v>
+      </c>
+      <c r="P54">
+        <v>-3.870595210305852</v>
+      </c>
+      <c r="Q54">
+        <v>-2.650595210305851</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1672503468844825</v>
+      </c>
+      <c r="T54">
+        <v>1.130824519618614</v>
+      </c>
+      <c r="U54">
+        <v>0.2388</v>
+      </c>
+      <c r="V54">
+        <v>0.04997388402052544</v>
+      </c>
+      <c r="W54">
+        <v>0.2268662364958985</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>0.2663831487683059</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.2002506094824189</v>
+      </c>
+      <c r="C55">
+        <v>-3.641290149563719</v>
+      </c>
+      <c r="D55">
+        <v>19.46770985043628</v>
+      </c>
+      <c r="E55">
+        <v>4.519000000000002</v>
+      </c>
+      <c r="F55">
+        <v>27.719</v>
+      </c>
+      <c r="G55">
+        <v>4.61</v>
+      </c>
+      <c r="H55">
+        <v>29.1</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>2.95</v>
+      </c>
+      <c r="K55">
+        <v>1.22</v>
+      </c>
+      <c r="L55">
+        <v>1.73</v>
+      </c>
+      <c r="M55">
+        <v>6.619297200000001</v>
+      </c>
+      <c r="N55">
+        <v>-4.889297200000001</v>
+      </c>
+      <c r="O55">
+        <v>-0.91723959396245</v>
+      </c>
+      <c r="P55">
+        <v>-3.972057606037551</v>
+      </c>
+      <c r="Q55">
+        <v>-2.752057606037551</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1699833329884077</v>
+      </c>
+      <c r="T55">
+        <v>1.154884615780712</v>
+      </c>
+      <c r="U55">
+        <v>0.2388</v>
+      </c>
+      <c r="V55">
+        <v>0.04903098054844005</v>
+      </c>
+      <c r="W55">
+        <v>0.2270914018450325</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>0.2613570516217339</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.2022506094824189</v>
+      </c>
+      <c r="C56">
+        <v>-4.402499231953595</v>
+      </c>
+      <c r="D56">
+        <v>19.22950076804641</v>
+      </c>
+      <c r="E56">
+        <v>5.042000000000002</v>
+      </c>
+      <c r="F56">
+        <v>28.242</v>
+      </c>
+      <c r="G56">
+        <v>4.61</v>
+      </c>
+      <c r="H56">
+        <v>29.1</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>2.95</v>
+      </c>
+      <c r="K56">
+        <v>1.22</v>
+      </c>
+      <c r="L56">
+        <v>1.73</v>
+      </c>
+      <c r="M56">
+        <v>6.7441896</v>
+      </c>
+      <c r="N56">
+        <v>-5.0141896</v>
+      </c>
+      <c r="O56">
+        <v>-0.9406695982307515</v>
+      </c>
+      <c r="P56">
+        <v>-4.073520001769248</v>
+      </c>
+      <c r="Q56">
+        <v>-2.853520001769248</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1728351445751122</v>
+      </c>
+      <c r="T56">
+        <v>1.179990803080292</v>
+      </c>
+      <c r="U56">
+        <v>0.2388</v>
+      </c>
+      <c r="V56">
+        <v>0.04812299942717264</v>
+      </c>
+      <c r="W56">
+        <v>0.2273082277367912</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>0.2565171062213316</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.2042506094824189</v>
+      </c>
+      <c r="C57">
+        <v>-5.157949276449678</v>
+      </c>
+      <c r="D57">
+        <v>18.99705072355032</v>
+      </c>
+      <c r="E57">
+        <v>5.565000000000001</v>
+      </c>
+      <c r="F57">
+        <v>28.765</v>
+      </c>
+      <c r="G57">
+        <v>4.61</v>
+      </c>
+      <c r="H57">
+        <v>29.1</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>2.95</v>
+      </c>
+      <c r="K57">
+        <v>1.22</v>
+      </c>
+      <c r="L57">
+        <v>1.73</v>
+      </c>
+      <c r="M57">
+        <v>6.869082000000001</v>
+      </c>
+      <c r="N57">
+        <v>-5.139082</v>
+      </c>
+      <c r="O57">
+        <v>-0.9640996024990532</v>
+      </c>
+      <c r="P57">
+        <v>-4.174982397500947</v>
+      </c>
+      <c r="Q57">
+        <v>-2.954982397500947</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.175813703343448</v>
+      </c>
+      <c r="T57">
+        <v>1.206212820926521</v>
+      </c>
+      <c r="U57">
+        <v>0.2388</v>
+      </c>
+      <c r="V57">
+        <v>0.04724803580122405</v>
+      </c>
+      <c r="W57">
+        <v>0.2275171690506677</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>0.2518531588354893</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.2062506094824189</v>
+      </c>
+      <c r="C58">
+        <v>-5.90784663779425</v>
+      </c>
+      <c r="D58">
+        <v>18.77015336220575</v>
+      </c>
+      <c r="E58">
+        <v>6.088000000000001</v>
+      </c>
+      <c r="F58">
+        <v>29.288</v>
+      </c>
+      <c r="G58">
+        <v>4.61</v>
+      </c>
+      <c r="H58">
+        <v>29.1</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>2.95</v>
+      </c>
+      <c r="K58">
+        <v>1.22</v>
+      </c>
+      <c r="L58">
+        <v>1.73</v>
+      </c>
+      <c r="M58">
+        <v>6.993974400000001</v>
+      </c>
+      <c r="N58">
+        <v>-5.2639744</v>
+      </c>
+      <c r="O58">
+        <v>-0.9875296067673551</v>
+      </c>
+      <c r="P58">
+        <v>-4.276444793232645</v>
+      </c>
+      <c r="Q58">
+        <v>-3.056444793232645</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1789276511467082</v>
+      </c>
+      <c r="T58">
+        <v>1.233626748674851</v>
+      </c>
+      <c r="U58">
+        <v>0.2388</v>
+      </c>
+      <c r="V58">
+        <v>0.04640432087620219</v>
+      </c>
+      <c r="W58">
+        <v>0.2277186481747629</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>0.2473557809991412</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.2082506094824189</v>
+      </c>
+      <c r="C59">
+        <v>-6.652387928433903</v>
+      </c>
+      <c r="D59">
+        <v>18.5486120715661</v>
+      </c>
+      <c r="E59">
+        <v>6.611000000000001</v>
+      </c>
+      <c r="F59">
+        <v>29.811</v>
+      </c>
+      <c r="G59">
+        <v>4.61</v>
+      </c>
+      <c r="H59">
+        <v>29.1</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>2.95</v>
+      </c>
+      <c r="K59">
+        <v>1.22</v>
+      </c>
+      <c r="L59">
+        <v>1.73</v>
+      </c>
+      <c r="M59">
+        <v>7.1188668</v>
+      </c>
+      <c r="N59">
+        <v>-5.388866800000001</v>
+      </c>
+      <c r="O59">
+        <v>-1.010959611035657</v>
+      </c>
+      <c r="P59">
+        <v>-4.377907188964343</v>
+      </c>
+      <c r="Q59">
+        <v>-3.157907188964343</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1821864337315154</v>
+      </c>
+      <c r="T59">
+        <v>1.26231574283008</v>
+      </c>
+      <c r="U59">
+        <v>0.2388</v>
+      </c>
+      <c r="V59">
+        <v>0.04559020998363724</v>
+      </c>
+      <c r="W59">
+        <v>0.2279130578559074</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>0.2430162058938931</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.2102506094824189</v>
+      </c>
+      <c r="C60">
+        <v>-7.391760586747118</v>
+      </c>
+      <c r="D60">
+        <v>18.33223941325288</v>
+      </c>
+      <c r="E60">
+        <v>7.133999999999997</v>
+      </c>
+      <c r="F60">
+        <v>30.334</v>
+      </c>
+      <c r="G60">
+        <v>4.61</v>
+      </c>
+      <c r="H60">
+        <v>29.1</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>2.95</v>
+      </c>
+      <c r="K60">
+        <v>1.22</v>
+      </c>
+      <c r="L60">
+        <v>1.73</v>
+      </c>
+      <c r="M60">
+        <v>7.2437592</v>
+      </c>
+      <c r="N60">
+        <v>-5.513759199999999</v>
+      </c>
+      <c r="O60">
+        <v>-1.034389615303958</v>
+      </c>
+      <c r="P60">
+        <v>-4.479369584696041</v>
+      </c>
+      <c r="Q60">
+        <v>-3.259369584696041</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1856003964394086</v>
+      </c>
+      <c r="T60">
+        <v>1.29237087956413</v>
+      </c>
+      <c r="U60">
+        <v>0.2388</v>
+      </c>
+      <c r="V60">
+        <v>0.04480417188047108</v>
+      </c>
+      <c r="W60">
+        <v>0.2281007637549435</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>0.2388262713095157</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.2122506094824188</v>
+      </c>
+      <c r="C61">
+        <v>-8.126143405959532</v>
+      </c>
+      <c r="D61">
+        <v>18.12085659404046</v>
+      </c>
+      <c r="E61">
+        <v>7.656999999999996</v>
+      </c>
+      <c r="F61">
+        <v>30.857</v>
+      </c>
+      <c r="G61">
+        <v>4.61</v>
+      </c>
+      <c r="H61">
+        <v>29.1</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>2.95</v>
+      </c>
+      <c r="K61">
+        <v>1.22</v>
+      </c>
+      <c r="L61">
+        <v>1.73</v>
+      </c>
+      <c r="M61">
+        <v>7.3686516</v>
+      </c>
+      <c r="N61">
+        <v>-5.638651599999999</v>
+      </c>
+      <c r="O61">
+        <v>-1.05781961957226</v>
+      </c>
+      <c r="P61">
+        <v>-4.580831980427739</v>
+      </c>
+      <c r="Q61">
+        <v>-3.360831980427739</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1891808939135405</v>
+      </c>
+      <c r="T61">
+        <v>1.323892120529108</v>
+      </c>
+      <c r="U61">
+        <v>0.2388</v>
+      </c>
+      <c r="V61">
+        <v>0.04404477913673428</v>
+      </c>
+      <c r="W61">
+        <v>0.2282821067421479</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>0.2347783684059646</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.2142506094824188</v>
+      </c>
+      <c r="C62">
+        <v>-8.855707026883927</v>
+      </c>
+      <c r="D62">
+        <v>17.91429297311607</v>
+      </c>
+      <c r="E62">
+        <v>8.179999999999996</v>
+      </c>
+      <c r="F62">
+        <v>31.38</v>
+      </c>
+      <c r="G62">
+        <v>4.61</v>
+      </c>
+      <c r="H62">
+        <v>29.1</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>2.95</v>
+      </c>
+      <c r="K62">
+        <v>1.22</v>
+      </c>
+      <c r="L62">
+        <v>1.73</v>
+      </c>
+      <c r="M62">
+        <v>7.493543999999999</v>
+      </c>
+      <c r="N62">
+        <v>-5.763544</v>
+      </c>
+      <c r="O62">
+        <v>-1.081249623840562</v>
+      </c>
+      <c r="P62">
+        <v>-4.682294376159438</v>
+      </c>
+      <c r="Q62">
+        <v>-3.462294376159437</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.192940416261379</v>
+      </c>
+      <c r="T62">
+        <v>1.356989423542336</v>
+      </c>
+      <c r="U62">
+        <v>0.2388</v>
+      </c>
+      <c r="V62">
+        <v>0.04331069948445538</v>
+      </c>
+      <c r="W62">
+        <v>0.2284574049631121</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>0.2308653955991984</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.2162506094824189</v>
+      </c>
+      <c r="C63">
+        <v>-9.580614397338934</v>
+      </c>
+      <c r="D63">
+        <v>17.71238560266107</v>
+      </c>
+      <c r="E63">
+        <v>8.702999999999999</v>
+      </c>
+      <c r="F63">
+        <v>31.903</v>
+      </c>
+      <c r="G63">
+        <v>4.61</v>
+      </c>
+      <c r="H63">
+        <v>29.1</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>2.95</v>
+      </c>
+      <c r="K63">
+        <v>1.22</v>
+      </c>
+      <c r="L63">
+        <v>1.73</v>
+      </c>
+      <c r="M63">
+        <v>7.6184364</v>
+      </c>
+      <c r="N63">
+        <v>-5.8884364</v>
+      </c>
+      <c r="O63">
+        <v>-1.104679628108864</v>
+      </c>
+      <c r="P63">
+        <v>-4.783756771891136</v>
+      </c>
+      <c r="Q63">
+        <v>-3.563756771891136</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1968927346270554</v>
+      </c>
+      <c r="T63">
+        <v>1.391784024145986</v>
+      </c>
+      <c r="U63">
+        <v>0.2388</v>
+      </c>
+      <c r="V63">
+        <v>0.04260068801749709</v>
+      </c>
+      <c r="W63">
+        <v>0.2286269557014217</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.2270807169828182</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.2182506094824189</v>
+      </c>
+      <c r="C64">
+        <v>-10.30102120084601</v>
+      </c>
+      <c r="D64">
+        <v>17.51497879915398</v>
+      </c>
+      <c r="E64">
+        <v>9.225999999999996</v>
+      </c>
+      <c r="F64">
+        <v>32.42599999999999</v>
+      </c>
+      <c r="G64">
+        <v>4.61</v>
+      </c>
+      <c r="H64">
+        <v>29.1</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>2.95</v>
+      </c>
+      <c r="K64">
+        <v>1.22</v>
+      </c>
+      <c r="L64">
+        <v>1.73</v>
+      </c>
+      <c r="M64">
+        <v>7.7433288</v>
+      </c>
+      <c r="N64">
+        <v>-6.0133288</v>
+      </c>
+      <c r="O64">
+        <v>-1.128109632377166</v>
+      </c>
+      <c r="P64">
+        <v>-4.885219167622834</v>
+      </c>
+      <c r="Q64">
+        <v>-3.665219167622834</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.20105306974882</v>
+      </c>
+      <c r="T64">
+        <v>1.428409919518248</v>
+      </c>
+      <c r="U64">
+        <v>0.2388</v>
+      </c>
+      <c r="V64">
+        <v>0.04191358014624715</v>
+      </c>
+      <c r="W64">
+        <v>0.2287910370610762</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.2234181247734178</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.2202506094824189</v>
+      </c>
+      <c r="C65">
+        <v>-11.01707625697523</v>
+      </c>
+      <c r="D65">
+        <v>17.32192374302477</v>
+      </c>
+      <c r="E65">
+        <v>9.748999999999999</v>
+      </c>
+      <c r="F65">
+        <v>32.949</v>
+      </c>
+      <c r="G65">
+        <v>4.61</v>
+      </c>
+      <c r="H65">
+        <v>29.1</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2.95</v>
+      </c>
+      <c r="K65">
+        <v>1.22</v>
+      </c>
+      <c r="L65">
+        <v>1.73</v>
+      </c>
+      <c r="M65">
+        <v>7.8682212</v>
+      </c>
+      <c r="N65">
+        <v>-6.1382212</v>
+      </c>
+      <c r="O65">
+        <v>-1.151539636645467</v>
+      </c>
+      <c r="P65">
+        <v>-4.986681563354533</v>
+      </c>
+      <c r="Q65">
+        <v>-3.766681563354533</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.2054382878501395</v>
+      </c>
+      <c r="T65">
+        <v>1.467015593018742</v>
+      </c>
+      <c r="U65">
+        <v>0.2388</v>
+      </c>
+      <c r="V65">
+        <v>0.04124828522329084</v>
+      </c>
+      <c r="W65">
+        <v>0.2289499094886782</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.2198718053325699</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.2222506094824188</v>
+      </c>
+      <c r="C66">
+        <v>-11.72892189550318</v>
+      </c>
+      <c r="D66">
+        <v>17.13307810449682</v>
+      </c>
+      <c r="E66">
+        <v>10.272</v>
+      </c>
+      <c r="F66">
+        <v>33.472</v>
+      </c>
+      <c r="G66">
+        <v>4.61</v>
+      </c>
+      <c r="H66">
+        <v>29.1</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2.95</v>
+      </c>
+      <c r="K66">
+        <v>1.22</v>
+      </c>
+      <c r="L66">
+        <v>1.73</v>
+      </c>
+      <c r="M66">
+        <v>7.993113600000001</v>
+      </c>
+      <c r="N66">
+        <v>-6.263113600000001</v>
+      </c>
+      <c r="O66">
+        <v>-1.174969640913769</v>
+      </c>
+      <c r="P66">
+        <v>-5.088143959086231</v>
+      </c>
+      <c r="Q66">
+        <v>-3.868143959086231</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.21006712917931</v>
+      </c>
+      <c r="T66">
+        <v>1.507766026158151</v>
+      </c>
+      <c r="U66">
+        <v>0.2388</v>
+      </c>
+      <c r="V66">
+        <v>0.04060378076667691</v>
+      </c>
+      <c r="W66">
+        <v>0.2291038171529176</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.2164363083742485</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.2242506094824188</v>
+      </c>
+      <c r="C67">
+        <v>-12.43669430636032</v>
+      </c>
+      <c r="D67">
+        <v>16.94830569363967</v>
+      </c>
+      <c r="E67">
+        <v>10.795</v>
+      </c>
+      <c r="F67">
+        <v>33.995</v>
+      </c>
+      <c r="G67">
+        <v>4.61</v>
+      </c>
+      <c r="H67">
+        <v>29.1</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2.95</v>
+      </c>
+      <c r="K67">
+        <v>1.22</v>
+      </c>
+      <c r="L67">
+        <v>1.73</v>
+      </c>
+      <c r="M67">
+        <v>8.118005999999999</v>
+      </c>
+      <c r="N67">
+        <v>-6.388005999999999</v>
+      </c>
+      <c r="O67">
+        <v>-1.198399645182071</v>
+      </c>
+      <c r="P67">
+        <v>-5.189606354817928</v>
+      </c>
+      <c r="Q67">
+        <v>-3.969606354817928</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.2149604757272903</v>
+      </c>
+      <c r="T67">
+        <v>1.550845055476956</v>
+      </c>
+      <c r="U67">
+        <v>0.2388</v>
+      </c>
+      <c r="V67">
+        <v>0.03997910721642035</v>
+      </c>
+      <c r="W67">
+        <v>0.2292529891967188</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.2131065190146448</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.2262506094824188</v>
+      </c>
+      <c r="C68">
+        <v>-13.1405238671757</v>
+      </c>
+      <c r="D68">
+        <v>16.7674761328243</v>
+      </c>
+      <c r="E68">
+        <v>11.318</v>
+      </c>
+      <c r="F68">
+        <v>34.518</v>
+      </c>
+      <c r="G68">
+        <v>4.61</v>
+      </c>
+      <c r="H68">
+        <v>29.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2.95</v>
+      </c>
+      <c r="K68">
+        <v>1.22</v>
+      </c>
+      <c r="L68">
+        <v>1.73</v>
+      </c>
+      <c r="M68">
+        <v>8.242898400000001</v>
+      </c>
+      <c r="N68">
+        <v>-6.512898400000001</v>
+      </c>
+      <c r="O68">
+        <v>-1.221829649450373</v>
+      </c>
+      <c r="P68">
+        <v>-5.291068750549628</v>
+      </c>
+      <c r="Q68">
+        <v>-4.071068750549628</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2201416661898576</v>
+      </c>
+      <c r="T68">
+        <v>1.596458145343925</v>
+      </c>
+      <c r="U68">
+        <v>0.2388</v>
+      </c>
+      <c r="V68">
+        <v>0.0393733631676867</v>
+      </c>
+      <c r="W68">
+        <v>0.2293976408755564</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.2098776323629077</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.2282506094824189</v>
+      </c>
+      <c r="C69">
+        <v>-13.84053545007462</v>
+      </c>
+      <c r="D69">
+        <v>16.59046454992538</v>
+      </c>
+      <c r="E69">
+        <v>11.841</v>
+      </c>
+      <c r="F69">
+        <v>35.041</v>
+      </c>
+      <c r="G69">
+        <v>4.61</v>
+      </c>
+      <c r="H69">
+        <v>29.1</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2.95</v>
+      </c>
+      <c r="K69">
+        <v>1.22</v>
+      </c>
+      <c r="L69">
+        <v>1.73</v>
+      </c>
+      <c r="M69">
+        <v>8.3677908</v>
+      </c>
+      <c r="N69">
+        <v>-6.637790799999999</v>
+      </c>
+      <c r="O69">
+        <v>-1.245259653718674</v>
+      </c>
+      <c r="P69">
+        <v>-5.392531146281325</v>
+      </c>
+      <c r="Q69">
+        <v>-4.172531146281324</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2256368681956109</v>
+      </c>
+      <c r="T69">
+        <v>1.644835664899801</v>
+      </c>
+      <c r="U69">
+        <v>0.2388</v>
+      </c>
+      <c r="V69">
+        <v>0.03878570103085556</v>
+      </c>
+      <c r="W69">
+        <v>0.2295379745938317</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.206745130387342</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.2302506094824189</v>
+      </c>
+      <c r="C70">
+        <v>-14.53684870924655</v>
+      </c>
+      <c r="D70">
+        <v>16.41715129075345</v>
+      </c>
+      <c r="E70">
+        <v>12.364</v>
+      </c>
+      <c r="F70">
+        <v>35.564</v>
+      </c>
+      <c r="G70">
+        <v>4.61</v>
+      </c>
+      <c r="H70">
+        <v>29.1</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2.95</v>
+      </c>
+      <c r="K70">
+        <v>1.22</v>
+      </c>
+      <c r="L70">
+        <v>1.73</v>
+      </c>
+      <c r="M70">
+        <v>8.4926832</v>
+      </c>
+      <c r="N70">
+        <v>-6.7626832</v>
+      </c>
+      <c r="O70">
+        <v>-1.268689657986976</v>
+      </c>
+      <c r="P70">
+        <v>-5.493993542013023</v>
+      </c>
+      <c r="Q70">
+        <v>-4.273993542013024</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2314755203267238</v>
+      </c>
+      <c r="T70">
+        <v>1.69623677942792</v>
+      </c>
+      <c r="U70">
+        <v>0.2388</v>
+      </c>
+      <c r="V70">
+        <v>0.03821532307451945</v>
+      </c>
+      <c r="W70">
+        <v>0.2296741808498048</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.2037047608228222</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.2322506094824189</v>
+      </c>
+      <c r="C71">
+        <v>-15.2295783506747</v>
+      </c>
+      <c r="D71">
+        <v>16.2474216493253</v>
+      </c>
+      <c r="E71">
+        <v>12.887</v>
+      </c>
+      <c r="F71">
+        <v>36.087</v>
+      </c>
+      <c r="G71">
+        <v>4.61</v>
+      </c>
+      <c r="H71">
+        <v>29.1</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2.95</v>
+      </c>
+      <c r="K71">
+        <v>1.22</v>
+      </c>
+      <c r="L71">
+        <v>1.73</v>
+      </c>
+      <c r="M71">
+        <v>8.617575600000002</v>
+      </c>
+      <c r="N71">
+        <v>-6.887575600000002</v>
+      </c>
+      <c r="O71">
+        <v>-1.292119662255278</v>
+      </c>
+      <c r="P71">
+        <v>-5.595455937744724</v>
+      </c>
+      <c r="Q71">
+        <v>-4.375455937744723</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.237690859692102</v>
+      </c>
+      <c r="T71">
+        <v>1.750954094893337</v>
+      </c>
+      <c r="U71">
+        <v>0.2388</v>
+      </c>
+      <c r="V71">
+        <v>0.03766147781256989</v>
+      </c>
+      <c r="W71">
+        <v>0.2298064390983583</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.2007525179123465</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.2342506094824189</v>
+      </c>
+      <c r="C72">
+        <v>-15.91883438530514</v>
+      </c>
+      <c r="D72">
+        <v>16.08116561469486</v>
+      </c>
+      <c r="E72">
+        <v>13.41</v>
+      </c>
+      <c r="F72">
+        <v>36.61</v>
+      </c>
+      <c r="G72">
+        <v>4.61</v>
+      </c>
+      <c r="H72">
+        <v>29.1</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2.95</v>
+      </c>
+      <c r="K72">
+        <v>1.22</v>
+      </c>
+      <c r="L72">
+        <v>1.73</v>
+      </c>
+      <c r="M72">
+        <v>8.742468000000001</v>
+      </c>
+      <c r="N72">
+        <v>-7.012468</v>
+      </c>
+      <c r="O72">
+        <v>-1.31554966652358</v>
+      </c>
+      <c r="P72">
+        <v>-5.69691833347642</v>
+      </c>
+      <c r="Q72">
+        <v>-4.476918333476419</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.244320555015172</v>
+      </c>
+      <c r="T72">
+        <v>1.809319231389782</v>
+      </c>
+      <c r="U72">
+        <v>0.2388</v>
+      </c>
+      <c r="V72">
+        <v>0.03712345670096175</v>
+      </c>
+      <c r="W72">
+        <v>0.2299349185398104</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.197884624799313</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.2362506094824188</v>
+      </c>
+      <c r="C73">
+        <v>-16.60472236682972</v>
+      </c>
+      <c r="D73">
+        <v>15.91827763317028</v>
+      </c>
+      <c r="E73">
+        <v>13.933</v>
+      </c>
+      <c r="F73">
+        <v>37.133</v>
+      </c>
+      <c r="G73">
+        <v>4.61</v>
+      </c>
+      <c r="H73">
+        <v>29.1</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2.95</v>
+      </c>
+      <c r="K73">
+        <v>1.22</v>
+      </c>
+      <c r="L73">
+        <v>1.73</v>
+      </c>
+      <c r="M73">
+        <v>8.867360399999999</v>
+      </c>
+      <c r="N73">
+        <v>-7.137360399999999</v>
+      </c>
+      <c r="O73">
+        <v>-1.338979670791881</v>
+      </c>
+      <c r="P73">
+        <v>-5.798380729208118</v>
+      </c>
+      <c r="Q73">
+        <v>-4.578380729208117</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2514074707053504</v>
+      </c>
+      <c r="T73">
+        <v>1.871709549713567</v>
+      </c>
+      <c r="U73">
+        <v>0.2388</v>
+      </c>
+      <c r="V73">
+        <v>0.03660059111362426</v>
+      </c>
+      <c r="W73">
+        <v>0.2300597788420665</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.1950975174077734</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.2382506094824188</v>
+      </c>
+      <c r="C74">
+        <v>-17.28734361516262</v>
+      </c>
+      <c r="D74">
+        <v>15.75865638483738</v>
+      </c>
+      <c r="E74">
+        <v>14.456</v>
+      </c>
+      <c r="F74">
+        <v>37.656</v>
+      </c>
+      <c r="G74">
+        <v>4.61</v>
+      </c>
+      <c r="H74">
+        <v>29.1</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2.95</v>
+      </c>
+      <c r="K74">
+        <v>1.22</v>
+      </c>
+      <c r="L74">
+        <v>1.73</v>
+      </c>
+      <c r="M74">
+        <v>8.992252800000001</v>
+      </c>
+      <c r="N74">
+        <v>-7.262252800000001</v>
+      </c>
+      <c r="O74">
+        <v>-1.362409675060183</v>
+      </c>
+      <c r="P74">
+        <v>-5.899843124939817</v>
+      </c>
+      <c r="Q74">
+        <v>-4.679843124939817</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2590005946591128</v>
+      </c>
+      <c r="T74">
+        <v>1.938556319346194</v>
+      </c>
+      <c r="U74">
+        <v>0.2388</v>
+      </c>
+      <c r="V74">
+        <v>0.03609224957037947</v>
+      </c>
+      <c r="W74">
+        <v>0.2301811708025934</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.1923878296659988</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2402506094824188</v>
+      </c>
+      <c r="C75">
+        <v>-17.96679542660489</v>
+      </c>
+      <c r="D75">
+        <v>15.60220457339511</v>
+      </c>
+      <c r="E75">
+        <v>14.979</v>
+      </c>
+      <c r="F75">
+        <v>38.17899999999999</v>
+      </c>
+      <c r="G75">
+        <v>4.61</v>
+      </c>
+      <c r="H75">
+        <v>29.1</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2.95</v>
+      </c>
+      <c r="K75">
+        <v>1.22</v>
+      </c>
+      <c r="L75">
+        <v>1.73</v>
+      </c>
+      <c r="M75">
+        <v>9.1171452</v>
+      </c>
+      <c r="N75">
+        <v>-7.387145199999999</v>
+      </c>
+      <c r="O75">
+        <v>-1.385839679328485</v>
+      </c>
+      <c r="P75">
+        <v>-6.001305520671514</v>
+      </c>
+      <c r="Q75">
+        <v>-4.781305520671514</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2671561722390799</v>
+      </c>
+      <c r="T75">
+        <v>2.010354701544201</v>
+      </c>
+      <c r="U75">
+        <v>0.2388</v>
+      </c>
+      <c r="V75">
+        <v>0.03559783519270305</v>
+      </c>
+      <c r="W75">
+        <v>0.2302992369559825</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.1897523799445467</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2422506094824188</v>
+      </c>
+      <c r="C76">
+        <v>-18.64317127161305</v>
+      </c>
+      <c r="D76">
+        <v>15.44882872838695</v>
+      </c>
+      <c r="E76">
+        <v>15.502</v>
+      </c>
+      <c r="F76">
+        <v>38.702</v>
+      </c>
+      <c r="G76">
+        <v>4.61</v>
+      </c>
+      <c r="H76">
+        <v>29.1</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2.95</v>
+      </c>
+      <c r="K76">
+        <v>1.22</v>
+      </c>
+      <c r="L76">
+        <v>1.73</v>
+      </c>
+      <c r="M76">
+        <v>9.2420376</v>
+      </c>
+      <c r="N76">
+        <v>-7.512037599999999</v>
+      </c>
+      <c r="O76">
+        <v>-1.409269683596787</v>
+      </c>
+      <c r="P76">
+        <v>-6.102767916403213</v>
+      </c>
+      <c r="Q76">
+        <v>-4.882767916403212</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.275939101940583</v>
+      </c>
+      <c r="T76">
+        <v>2.087676036218978</v>
+      </c>
+      <c r="U76">
+        <v>0.2388</v>
+      </c>
+      <c r="V76">
+        <v>0.03511678336577463</v>
+      </c>
+      <c r="W76">
+        <v>0.230414112132253</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.1871881585939448</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2442506094824188</v>
+      </c>
+      <c r="C77">
+        <v>-19.31656098101626</v>
+      </c>
+      <c r="D77">
+        <v>15.29843901898374</v>
+      </c>
+      <c r="E77">
+        <v>16.025</v>
+      </c>
+      <c r="F77">
+        <v>39.22499999999999</v>
+      </c>
+      <c r="G77">
+        <v>4.61</v>
+      </c>
+      <c r="H77">
+        <v>29.1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2.95</v>
+      </c>
+      <c r="K77">
+        <v>1.22</v>
+      </c>
+      <c r="L77">
+        <v>1.73</v>
+      </c>
+      <c r="M77">
+        <v>9.36693</v>
+      </c>
+      <c r="N77">
+        <v>-7.63693</v>
+      </c>
+      <c r="O77">
+        <v>-1.432699687865088</v>
+      </c>
+      <c r="P77">
+        <v>-6.204230312134911</v>
+      </c>
+      <c r="Q77">
+        <v>-4.98423031213491</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.2854246660182064</v>
+      </c>
+      <c r="T77">
+        <v>2.171183077667738</v>
+      </c>
+      <c r="U77">
+        <v>0.2388</v>
+      </c>
+      <c r="V77">
+        <v>0.03464855958756431</v>
+      </c>
+      <c r="W77">
+        <v>0.2305259239704897</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.1846923164793588</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2462506094824188</v>
+      </c>
+      <c r="C78">
+        <v>-19.98705092146187</v>
+      </c>
+      <c r="D78">
+        <v>15.15094907853813</v>
+      </c>
+      <c r="E78">
+        <v>16.548</v>
+      </c>
+      <c r="F78">
+        <v>39.748</v>
+      </c>
+      <c r="G78">
+        <v>4.61</v>
+      </c>
+      <c r="H78">
+        <v>29.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2.95</v>
+      </c>
+      <c r="K78">
+        <v>1.22</v>
+      </c>
+      <c r="L78">
+        <v>1.73</v>
+      </c>
+      <c r="M78">
+        <v>9.4918224</v>
+      </c>
+      <c r="N78">
+        <v>-7.7618224</v>
+      </c>
+      <c r="O78">
+        <v>-1.45612969213339</v>
+      </c>
+      <c r="P78">
+        <v>-6.305692707866609</v>
+      </c>
+      <c r="Q78">
+        <v>-5.08569270786661</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.295700693768965</v>
+      </c>
+      <c r="T78">
+        <v>2.261649039237227</v>
+      </c>
+      <c r="U78">
+        <v>0.2388</v>
+      </c>
+      <c r="V78">
+        <v>0.03419265748772793</v>
+      </c>
+      <c r="W78">
+        <v>0.2306347933919306</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.1822621544204198</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2482506094824188</v>
+      </c>
+      <c r="C79">
+        <v>-20.65472416080912</v>
+      </c>
+      <c r="D79">
+        <v>15.00627583919088</v>
+      </c>
+      <c r="E79">
+        <v>17.071</v>
+      </c>
+      <c r="F79">
+        <v>40.271</v>
+      </c>
+      <c r="G79">
+        <v>4.61</v>
+      </c>
+      <c r="H79">
+        <v>29.1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2.95</v>
+      </c>
+      <c r="K79">
+        <v>1.22</v>
+      </c>
+      <c r="L79">
+        <v>1.73</v>
+      </c>
+      <c r="M79">
+        <v>9.6167148</v>
+      </c>
+      <c r="N79">
+        <v>-7.8867148</v>
+      </c>
+      <c r="O79">
+        <v>-1.479559696401692</v>
+      </c>
+      <c r="P79">
+        <v>-6.407155103598308</v>
+      </c>
+      <c r="Q79">
+        <v>-5.187155103598307</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.3068702891502244</v>
+      </c>
+      <c r="T79">
+        <v>2.359981606160584</v>
+      </c>
+      <c r="U79">
+        <v>0.2388</v>
+      </c>
+      <c r="V79">
+        <v>0.03374859700087432</v>
+      </c>
+      <c r="W79">
+        <v>0.2307408350361912</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.179895113453921</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2502506094824188</v>
+      </c>
+      <c r="C80">
+        <v>-21.31966062413662</v>
+      </c>
+      <c r="D80">
+        <v>14.86433937586337</v>
+      </c>
+      <c r="E80">
+        <v>17.594</v>
+      </c>
+      <c r="F80">
+        <v>40.794</v>
+      </c>
+      <c r="G80">
+        <v>4.61</v>
+      </c>
+      <c r="H80">
+        <v>29.1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2.95</v>
+      </c>
+      <c r="K80">
+        <v>1.22</v>
+      </c>
+      <c r="L80">
+        <v>1.73</v>
+      </c>
+      <c r="M80">
+        <v>9.741607199999999</v>
+      </c>
+      <c r="N80">
+        <v>-8.011607199999998</v>
+      </c>
+      <c r="O80">
+        <v>-1.502989700669993</v>
+      </c>
+      <c r="P80">
+        <v>-6.508617499330005</v>
+      </c>
+      <c r="Q80">
+        <v>-5.288617499330005</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3190553022934164</v>
+      </c>
+      <c r="T80">
+        <v>2.467253497349702</v>
+      </c>
+      <c r="U80">
+        <v>0.2388</v>
+      </c>
+      <c r="V80">
+        <v>0.03331592268035029</v>
+      </c>
+      <c r="W80">
+        <v>0.2308441576639323</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.1775887658455373</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2522506094824188</v>
+      </c>
+      <c r="C81">
+        <v>-21.98193724097935</v>
+      </c>
+      <c r="D81">
+        <v>14.72506275902065</v>
+      </c>
+      <c r="E81">
+        <v>18.117</v>
+      </c>
+      <c r="F81">
+        <v>41.317</v>
+      </c>
+      <c r="G81">
+        <v>4.61</v>
+      </c>
+      <c r="H81">
+        <v>29.1</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2.95</v>
+      </c>
+      <c r="K81">
+        <v>1.22</v>
+      </c>
+      <c r="L81">
+        <v>1.73</v>
+      </c>
+      <c r="M81">
+        <v>9.866499600000001</v>
+      </c>
+      <c r="N81">
+        <v>-8.1364996</v>
+      </c>
+      <c r="O81">
+        <v>-1.526419704938296</v>
+      </c>
+      <c r="P81">
+        <v>-6.610079895061705</v>
+      </c>
+      <c r="Q81">
+        <v>-5.390079895061705</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3324007928788172</v>
+      </c>
+      <c r="T81">
+        <v>2.58474175912826</v>
+      </c>
+      <c r="U81">
+        <v>0.2388</v>
+      </c>
+      <c r="V81">
+        <v>0.03289420214009268</v>
+      </c>
+      <c r="W81">
+        <v>0.2309448645289459</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.1753408067842014</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2542506094824188</v>
+      </c>
+      <c r="C82">
+        <v>-22.64162808436471</v>
+      </c>
+      <c r="D82">
+        <v>14.5883719156353</v>
+      </c>
+      <c r="E82">
+        <v>18.64</v>
+      </c>
+      <c r="F82">
+        <v>41.84</v>
+      </c>
+      <c r="G82">
+        <v>4.61</v>
+      </c>
+      <c r="H82">
+        <v>29.1</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2.95</v>
+      </c>
+      <c r="K82">
+        <v>1.22</v>
+      </c>
+      <c r="L82">
+        <v>1.73</v>
+      </c>
+      <c r="M82">
+        <v>9.991392000000001</v>
+      </c>
+      <c r="N82">
+        <v>-8.261392000000001</v>
+      </c>
+      <c r="O82">
+        <v>-1.549849709206597</v>
+      </c>
+      <c r="P82">
+        <v>-6.711542290793403</v>
+      </c>
+      <c r="Q82">
+        <v>-5.491542290793403</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3470808325227581</v>
+      </c>
+      <c r="T82">
+        <v>2.713978847084673</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.03248302461334153</v>
+      </c>
+      <c r="W82">
+        <v>0.2310430537223341</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.1731490466993989</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2562506094824188</v>
+      </c>
+      <c r="C83">
+        <v>-23.29880450217616</v>
+      </c>
+      <c r="D83">
+        <v>14.45419549782383</v>
+      </c>
+      <c r="E83">
+        <v>19.163</v>
+      </c>
+      <c r="F83">
+        <v>42.363</v>
+      </c>
+      <c r="G83">
+        <v>4.61</v>
+      </c>
+      <c r="H83">
+        <v>29.1</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2.95</v>
+      </c>
+      <c r="K83">
+        <v>1.22</v>
+      </c>
+      <c r="L83">
+        <v>1.73</v>
+      </c>
+      <c r="M83">
+        <v>10.1162844</v>
+      </c>
+      <c r="N83">
+        <v>-8.386284399999999</v>
+      </c>
+      <c r="O83">
+        <v>-1.573279713474899</v>
+      </c>
+      <c r="P83">
+        <v>-6.8130046865251</v>
+      </c>
+      <c r="Q83">
+        <v>-5.5930046865251</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.3633061394976401</v>
+      </c>
+      <c r="T83">
+        <v>2.856819839036497</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.03208199961811509</v>
+      </c>
+      <c r="W83">
+        <v>0.2311388184911941</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.1710114041475544</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2582506094824188</v>
+      </c>
+      <c r="C84">
+        <v>-23.95353524133351</v>
+      </c>
+      <c r="D84">
+        <v>14.32246475866649</v>
+      </c>
+      <c r="E84">
+        <v>19.686</v>
+      </c>
+      <c r="F84">
+        <v>42.886</v>
+      </c>
+      <c r="G84">
+        <v>4.61</v>
+      </c>
+      <c r="H84">
+        <v>29.1</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2.95</v>
+      </c>
+      <c r="K84">
+        <v>1.22</v>
+      </c>
+      <c r="L84">
+        <v>1.73</v>
+      </c>
+      <c r="M84">
+        <v>10.2411768</v>
+      </c>
+      <c r="N84">
+        <v>-8.511176800000001</v>
+      </c>
+      <c r="O84">
+        <v>-1.596709717743201</v>
+      </c>
+      <c r="P84">
+        <v>-6.914467082256801</v>
+      </c>
+      <c r="Q84">
+        <v>-5.6944670822568</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3813342583586201</v>
+      </c>
+      <c r="T84">
+        <v>3.015532052316303</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.0316907557203332</v>
+      </c>
+      <c r="W84">
+        <v>0.2312322475339844</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.1689258992189258</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2602506094824188</v>
+      </c>
+      <c r="C85">
+        <v>-24.60588656524398</v>
+      </c>
+      <c r="D85">
+        <v>14.19311343475602</v>
+      </c>
+      <c r="E85">
+        <v>20.209</v>
+      </c>
+      <c r="F85">
+        <v>43.409</v>
+      </c>
+      <c r="G85">
+        <v>4.61</v>
+      </c>
+      <c r="H85">
+        <v>29.1</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2.95</v>
+      </c>
+      <c r="K85">
+        <v>1.22</v>
+      </c>
+      <c r="L85">
+        <v>1.73</v>
+      </c>
+      <c r="M85">
+        <v>10.3660692</v>
+      </c>
+      <c r="N85">
+        <v>-8.6360692</v>
+      </c>
+      <c r="O85">
+        <v>-1.620139722011503</v>
+      </c>
+      <c r="P85">
+        <v>-7.015929477988497</v>
+      </c>
+      <c r="Q85">
+        <v>-5.795929477988496</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.4014833323797155</v>
+      </c>
+      <c r="T85">
+        <v>3.192916290687851</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.03130893938635328</v>
+      </c>
+      <c r="W85">
+        <v>0.2313234252745389</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.1668906474211074</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2622506094824189</v>
+      </c>
+      <c r="C86">
+        <v>-25.25592236494604</v>
+      </c>
+      <c r="D86">
+        <v>14.06607763505395</v>
+      </c>
+      <c r="E86">
+        <v>20.732</v>
+      </c>
+      <c r="F86">
+        <v>43.932</v>
+      </c>
+      <c r="G86">
+        <v>4.61</v>
+      </c>
+      <c r="H86">
+        <v>29.1</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2.95</v>
+      </c>
+      <c r="K86">
+        <v>1.22</v>
+      </c>
+      <c r="L86">
+        <v>1.73</v>
+      </c>
+      <c r="M86">
+        <v>10.4909616</v>
+      </c>
+      <c r="N86">
+        <v>-8.760961599999998</v>
+      </c>
+      <c r="O86">
+        <v>-1.643569726279804</v>
+      </c>
+      <c r="P86">
+        <v>-7.117391873720194</v>
+      </c>
+      <c r="Q86">
+        <v>-5.897391873720194</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4241510406534474</v>
+      </c>
+      <c r="T86">
+        <v>3.39247355885584</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.03093621391746813</v>
+      </c>
+      <c r="W86">
+        <v>0.2314124321165086</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.1649038539994275</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2642506094824189</v>
+      </c>
+      <c r="C87">
+        <v>-25.90370426433719</v>
+      </c>
+      <c r="D87">
+        <v>13.94129573566281</v>
+      </c>
+      <c r="E87">
+        <v>21.255</v>
+      </c>
+      <c r="F87">
+        <v>44.455</v>
+      </c>
+      <c r="G87">
+        <v>4.61</v>
+      </c>
+      <c r="H87">
+        <v>29.1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>2.95</v>
+      </c>
+      <c r="K87">
+        <v>1.22</v>
+      </c>
+      <c r="L87">
+        <v>1.73</v>
+      </c>
+      <c r="M87">
+        <v>10.615854</v>
+      </c>
+      <c r="N87">
+        <v>-8.885854</v>
+      </c>
+      <c r="O87">
+        <v>-1.666999730548106</v>
+      </c>
+      <c r="P87">
+        <v>-7.218854269451894</v>
+      </c>
+      <c r="Q87">
+        <v>-5.998854269451893</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4498411100303439</v>
+      </c>
+      <c r="T87">
+        <v>3.618638462779562</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.03057225845961556</v>
+      </c>
+      <c r="W87">
+        <v>0.2314993446798438</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.1629638086582578</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2662506094824189</v>
+      </c>
+      <c r="C88">
+        <v>-26.54929171985017</v>
+      </c>
+      <c r="D88">
+        <v>13.81870828014983</v>
+      </c>
+      <c r="E88">
+        <v>21.778</v>
+      </c>
+      <c r="F88">
+        <v>44.97799999999999</v>
+      </c>
+      <c r="G88">
+        <v>4.61</v>
+      </c>
+      <c r="H88">
+        <v>29.1</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>2.95</v>
+      </c>
+      <c r="K88">
+        <v>1.22</v>
+      </c>
+      <c r="L88">
+        <v>1.73</v>
+      </c>
+      <c r="M88">
+        <v>10.7407464</v>
+      </c>
+      <c r="N88">
+        <v>-9.010746399999999</v>
+      </c>
+      <c r="O88">
+        <v>-1.690429734816408</v>
+      </c>
+      <c r="P88">
+        <v>-7.320316665183591</v>
+      </c>
+      <c r="Q88">
+        <v>-6.100316665183591</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4792011893182257</v>
+      </c>
+      <c r="T88">
+        <v>3.877112638692389</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.03021676708217818</v>
+      </c>
+      <c r="W88">
+        <v>0.2315842360207759</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.1610688806506037</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2682506094824189</v>
+      </c>
+      <c r="C89">
+        <v>-27.1927421149162</v>
+      </c>
+      <c r="D89">
+        <v>13.69825788508379</v>
+      </c>
+      <c r="E89">
+        <v>22.301</v>
+      </c>
+      <c r="F89">
+        <v>45.501</v>
+      </c>
+      <c r="G89">
+        <v>4.61</v>
+      </c>
+      <c r="H89">
+        <v>29.1</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>2.95</v>
+      </c>
+      <c r="K89">
+        <v>1.22</v>
+      </c>
+      <c r="L89">
+        <v>1.73</v>
+      </c>
+      <c r="M89">
+        <v>10.8656388</v>
+      </c>
+      <c r="N89">
+        <v>-9.135638799999999</v>
+      </c>
+      <c r="O89">
+        <v>-1.713859739084709</v>
+      </c>
+      <c r="P89">
+        <v>-7.42177906091529</v>
+      </c>
+      <c r="Q89">
+        <v>-6.201779060915289</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.5130782038811661</v>
+      </c>
+      <c r="T89">
+        <v>4.175352072437956</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.02986944792031406</v>
+      </c>
+      <c r="W89">
+        <v>0.231667175836629</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.1592175142063438</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2702506094824189</v>
+      </c>
+      <c r="C90">
+        <v>-27.83411084953061</v>
+      </c>
+      <c r="D90">
+        <v>13.57988915046939</v>
+      </c>
+      <c r="E90">
+        <v>22.824</v>
+      </c>
+      <c r="F90">
+        <v>46.024</v>
+      </c>
+      <c r="G90">
+        <v>4.61</v>
+      </c>
+      <c r="H90">
+        <v>29.1</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>2.95</v>
+      </c>
+      <c r="K90">
+        <v>1.22</v>
+      </c>
+      <c r="L90">
+        <v>1.73</v>
+      </c>
+      <c r="M90">
+        <v>10.9905312</v>
+      </c>
+      <c r="N90">
+        <v>-9.260531200000001</v>
+      </c>
+      <c r="O90">
+        <v>-1.737289743353012</v>
+      </c>
+      <c r="P90">
+        <v>-7.523241456646989</v>
+      </c>
+      <c r="Q90">
+        <v>-6.303241456646989</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5526013875379301</v>
+      </c>
+      <c r="T90">
+        <v>4.523298078474454</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.02953002237576503</v>
+      </c>
+      <c r="W90">
+        <v>0.2317482306566673</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.1574082242721808</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2722506094824189</v>
+      </c>
+      <c r="C91">
+        <v>-28.4734514252145</v>
+      </c>
+      <c r="D91">
+        <v>13.4635485747855</v>
+      </c>
+      <c r="E91">
+        <v>23.347</v>
+      </c>
+      <c r="F91">
+        <v>46.547</v>
+      </c>
+      <c r="G91">
+        <v>4.61</v>
+      </c>
+      <c r="H91">
+        <v>29.1</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>2.95</v>
+      </c>
+      <c r="K91">
+        <v>1.22</v>
+      </c>
+      <c r="L91">
+        <v>1.73</v>
+      </c>
+      <c r="M91">
+        <v>11.1154236</v>
+      </c>
+      <c r="N91">
+        <v>-9.385423599999999</v>
+      </c>
+      <c r="O91">
+        <v>-1.760719747621313</v>
+      </c>
+      <c r="P91">
+        <v>-7.624703852378686</v>
+      </c>
+      <c r="Q91">
+        <v>-6.404703852378686</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5993106045868328</v>
+      </c>
+      <c r="T91">
+        <v>4.934506994699404</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.02919822437154295</v>
+      </c>
+      <c r="W91">
+        <v>0.2318274640200756</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.1556395925387856</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2742506094824189</v>
+      </c>
+      <c r="C92">
+        <v>-29.11081552564628</v>
+      </c>
+      <c r="D92">
+        <v>13.34918447435372</v>
+      </c>
+      <c r="E92">
+        <v>23.87</v>
+      </c>
+      <c r="F92">
+        <v>47.07</v>
+      </c>
+      <c r="G92">
+        <v>4.61</v>
+      </c>
+      <c r="H92">
+        <v>29.1</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>2.95</v>
+      </c>
+      <c r="K92">
+        <v>1.22</v>
+      </c>
+      <c r="L92">
+        <v>1.73</v>
+      </c>
+      <c r="M92">
+        <v>11.240316</v>
+      </c>
+      <c r="N92">
+        <v>-9.510316</v>
+      </c>
+      <c r="O92">
+        <v>-1.784149751889615</v>
+      </c>
+      <c r="P92">
+        <v>-7.726166248110385</v>
+      </c>
+      <c r="Q92">
+        <v>-6.506166248110384</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6553616650455163</v>
+      </c>
+      <c r="T92">
+        <v>5.427957694169346</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.02887379965630359</v>
+      </c>
+      <c r="W92">
+        <v>0.2319049366420747</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.153910263732799</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2762506094824189</v>
+      </c>
+      <c r="C93">
+        <v>-29.74625309321834</v>
+      </c>
+      <c r="D93">
+        <v>13.23674690678165</v>
+      </c>
+      <c r="E93">
+        <v>24.393</v>
+      </c>
+      <c r="F93">
+        <v>47.593</v>
+      </c>
+      <c r="G93">
+        <v>4.61</v>
+      </c>
+      <c r="H93">
+        <v>29.1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>2.95</v>
+      </c>
+      <c r="K93">
+        <v>1.22</v>
+      </c>
+      <c r="L93">
+        <v>1.73</v>
+      </c>
+      <c r="M93">
+        <v>11.3652084</v>
+      </c>
+      <c r="N93">
+        <v>-9.6352084</v>
+      </c>
+      <c r="O93">
+        <v>-1.807579756157917</v>
+      </c>
+      <c r="P93">
+        <v>-7.827628643842083</v>
+      </c>
+      <c r="Q93">
+        <v>-6.607628643842082</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.7238685167172403</v>
+      </c>
+      <c r="T93">
+        <v>6.031064104632606</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.02855650515458596</v>
+      </c>
+      <c r="W93">
+        <v>0.2319807065690849</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.1522189421533177</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2782506094824189</v>
+      </c>
+      <c r="C94">
+        <v>-30.37981240175711</v>
+      </c>
+      <c r="D94">
+        <v>13.12618759824289</v>
+      </c>
+      <c r="E94">
+        <v>24.916</v>
+      </c>
+      <c r="F94">
+        <v>48.116</v>
+      </c>
+      <c r="G94">
+        <v>4.61</v>
+      </c>
+      <c r="H94">
+        <v>29.1</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>2.95</v>
+      </c>
+      <c r="K94">
+        <v>1.22</v>
+      </c>
+      <c r="L94">
+        <v>1.73</v>
+      </c>
+      <c r="M94">
+        <v>11.4901008</v>
+      </c>
+      <c r="N94">
+        <v>-9.7601008</v>
+      </c>
+      <c r="O94">
+        <v>-1.831009760426219</v>
+      </c>
+      <c r="P94">
+        <v>-7.929091039573781</v>
+      </c>
+      <c r="Q94">
+        <v>-6.709091039573782</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.8095020813068954</v>
+      </c>
+      <c r="T94">
+        <v>6.784947117711684</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.02824610835942742</v>
+      </c>
+      <c r="W94">
+        <v>0.2320548293237688</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.1505643884342599</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2802506094824189</v>
+      </c>
+      <c r="C95">
+        <v>-31.01154012562893</v>
+      </c>
+      <c r="D95">
+        <v>13.01745987437107</v>
+      </c>
+      <c r="E95">
+        <v>25.439</v>
+      </c>
+      <c r="F95">
+        <v>48.639</v>
+      </c>
+      <c r="G95">
+        <v>4.61</v>
+      </c>
+      <c r="H95">
+        <v>29.1</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>2.95</v>
+      </c>
+      <c r="K95">
+        <v>1.22</v>
+      </c>
+      <c r="L95">
+        <v>1.73</v>
+      </c>
+      <c r="M95">
+        <v>11.6149932</v>
+      </c>
+      <c r="N95">
+        <v>-9.8849932</v>
+      </c>
+      <c r="O95">
+        <v>-1.85443976469452</v>
+      </c>
+      <c r="P95">
+        <v>-8.03055343530548</v>
+      </c>
+      <c r="Q95">
+        <v>-6.810553435305479</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.9196023786364522</v>
+      </c>
+      <c r="T95">
+        <v>7.754225277384784</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.02794238676416476</v>
+      </c>
+      <c r="W95">
+        <v>0.2321273580407175</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.1489454165156119</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2822506094824189</v>
+      </c>
+      <c r="C96">
+        <v>-31.64148140543962</v>
+      </c>
+      <c r="D96">
+        <v>12.91051859456038</v>
+      </c>
+      <c r="E96">
+        <v>25.962</v>
+      </c>
+      <c r="F96">
+        <v>49.162</v>
+      </c>
+      <c r="G96">
+        <v>4.61</v>
+      </c>
+      <c r="H96">
+        <v>29.1</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>2.95</v>
+      </c>
+      <c r="K96">
+        <v>1.22</v>
+      </c>
+      <c r="L96">
+        <v>1.73</v>
+      </c>
+      <c r="M96">
+        <v>11.7398856</v>
+      </c>
+      <c r="N96">
+        <v>-10.0098856</v>
+      </c>
+      <c r="O96">
+        <v>-1.877869768962822</v>
+      </c>
+      <c r="P96">
+        <v>-8.132015831037178</v>
+      </c>
+      <c r="Q96">
+        <v>-6.912015831037177</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.066402775075861</v>
+      </c>
+      <c r="T96">
+        <v>9.046596156948915</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.02764512733050343</v>
+      </c>
+      <c r="W96">
+        <v>0.2321983435934758</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.1473608908079991</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2842506094824188</v>
+      </c>
+      <c r="C97">
+        <v>-32.26967991052204</v>
+      </c>
+      <c r="D97">
+        <v>12.80532008947796</v>
+      </c>
+      <c r="E97">
+        <v>26.485</v>
+      </c>
+      <c r="F97">
+        <v>49.685</v>
+      </c>
+      <c r="G97">
+        <v>4.61</v>
+      </c>
+      <c r="H97">
+        <v>29.1</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>2.95</v>
+      </c>
+      <c r="K97">
+        <v>1.22</v>
+      </c>
+      <c r="L97">
+        <v>1.73</v>
+      </c>
+      <c r="M97">
+        <v>11.864778</v>
+      </c>
+      <c r="N97">
+        <v>-10.134778</v>
+      </c>
+      <c r="O97">
+        <v>-1.901299773231124</v>
+      </c>
+      <c r="P97">
+        <v>-8.233478226768877</v>
+      </c>
+      <c r="Q97">
+        <v>-7.013478226768877</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.271923330091034</v>
+      </c>
+      <c r="T97">
+        <v>10.8559153883387</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.02735412599018234</v>
+      </c>
+      <c r="W97">
+        <v>0.2322678347135445</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.1458097235363359</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2862506094824189</v>
+      </c>
+      <c r="C98">
+        <v>-32.89617789839334</v>
+      </c>
+      <c r="D98">
+        <v>12.70182210160666</v>
+      </c>
+      <c r="E98">
+        <v>27.008</v>
+      </c>
+      <c r="F98">
+        <v>50.208</v>
+      </c>
+      <c r="G98">
+        <v>4.61</v>
+      </c>
+      <c r="H98">
+        <v>29.1</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2.95</v>
+      </c>
+      <c r="K98">
+        <v>1.22</v>
+      </c>
+      <c r="L98">
+        <v>1.73</v>
+      </c>
+      <c r="M98">
+        <v>11.9896704</v>
+      </c>
+      <c r="N98">
+        <v>-10.2596704</v>
+      </c>
+      <c r="O98">
+        <v>-1.924729777499425</v>
+      </c>
+      <c r="P98">
+        <v>-8.334940622500573</v>
+      </c>
+      <c r="Q98">
+        <v>-7.114940622500573</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.580204162613789</v>
+      </c>
+      <c r="T98">
+        <v>13.56989423542335</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.02706918717778461</v>
+      </c>
+      <c r="W98">
+        <v>0.2323358781019451</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.1442908722494991</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2882506094824189</v>
+      </c>
+      <c r="C99">
+        <v>-33.5210162713519</v>
+      </c>
+      <c r="D99">
+        <v>12.59998372864809</v>
+      </c>
+      <c r="E99">
+        <v>27.531</v>
+      </c>
+      <c r="F99">
+        <v>50.73099999999999</v>
+      </c>
+      <c r="G99">
+        <v>4.61</v>
+      </c>
+      <c r="H99">
+        <v>29.1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>2.95</v>
+      </c>
+      <c r="K99">
+        <v>1.22</v>
+      </c>
+      <c r="L99">
+        <v>1.73</v>
+      </c>
+      <c r="M99">
+        <v>12.1145628</v>
+      </c>
+      <c r="N99">
+        <v>-10.3845628</v>
+      </c>
+      <c r="O99">
+        <v>-1.948159781767727</v>
+      </c>
+      <c r="P99">
+        <v>-8.436403018232273</v>
+      </c>
+      <c r="Q99">
+        <v>-7.216403018232272</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>2.094005550151719</v>
+      </c>
+      <c r="T99">
+        <v>18.0931923138978</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.02679012339244663</v>
+      </c>
+      <c r="W99">
+        <v>0.2324025185338838</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.1428033374840403</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2902506094824189</v>
+      </c>
+      <c r="C100">
+        <v>-34.14423463037345</v>
+      </c>
+      <c r="D100">
+        <v>12.49976536962654</v>
+      </c>
+      <c r="E100">
+        <v>28.054</v>
+      </c>
+      <c r="F100">
+        <v>51.254</v>
+      </c>
+      <c r="G100">
+        <v>4.61</v>
+      </c>
+      <c r="H100">
+        <v>29.1</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>2.95</v>
+      </c>
+      <c r="K100">
+        <v>1.22</v>
+      </c>
+      <c r="L100">
+        <v>1.73</v>
+      </c>
+      <c r="M100">
+        <v>12.2394552</v>
+      </c>
+      <c r="N100">
+        <v>-10.5094552</v>
+      </c>
+      <c r="O100">
+        <v>-1.971589786036029</v>
+      </c>
+      <c r="P100">
+        <v>-8.537865413963971</v>
+      </c>
+      <c r="Q100">
+        <v>-7.31786541396397</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>3.121608325227578</v>
+      </c>
+      <c r="T100">
+        <v>27.1397884708467</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.02651675478640125</v>
+      </c>
+      <c r="W100">
+        <v>0.2324677989570074</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.1413461605709379</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2922506094824189</v>
+      </c>
+      <c r="C101">
+        <v>-34.7658713264552</v>
+      </c>
+      <c r="D101">
+        <v>12.40112867354479</v>
+      </c>
+      <c r="E101">
+        <v>28.57699999999999</v>
+      </c>
+      <c r="F101">
+        <v>51.77699999999999</v>
+      </c>
+      <c r="G101">
+        <v>4.61</v>
+      </c>
+      <c r="H101">
+        <v>29.1</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>2.95</v>
+      </c>
+      <c r="K101">
+        <v>1.22</v>
+      </c>
+      <c r="L101">
+        <v>1.73</v>
+      </c>
+      <c r="M101">
+        <v>12.3643476</v>
+      </c>
+      <c r="N101">
+        <v>-10.6343476</v>
+      </c>
+      <c r="O101">
+        <v>-1.995019790304331</v>
+      </c>
+      <c r="P101">
+        <v>-8.639327809695668</v>
+      </c>
+      <c r="Q101">
+        <v>-7.419327809695668</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>6.204416650455156</v>
+      </c>
+      <c r="T101">
+        <v>54.2795769416934</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.02624890877845781</v>
+      </c>
+      <c r="W101">
+        <v>0.2325317605837043</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.1399184215752718</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
